--- a/output/full_scan/batch_seq7_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-18.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1016.903837538405</v>
+        <v>1226.903837538405</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>245.5</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.25870188280011</v>
+        <v>65.25870188023433</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.79605444396801</v>
+        <v>25.7960543927107</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.193897725982851</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.8056264631379548</v>
+        <v>0.8056264634813708</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6742</v>
+        <v>6725</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>905.125659677564</v>
+        <v>1165.417690292468</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>69</v>
+        <v>367</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.386397198891</v>
+        <v>66.43892391066322</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33.70543683886181</v>
+        <v>18.25406982513641</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.720614138820118</v>
+        <v>3.445540674421005</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,11 +623,11 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3901265353956415</v>
+        <v>5.875826054079186</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>898.7615697388197</v>
+        <v>1098.76156973882</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>143</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>71.31343204942726</v>
+        <v>71.31343204612867</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>28.10345490495544</v>
+        <v>28.10345490364681</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.570403100250089</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.9698423109469232</v>
+        <v>0.9698423111758744</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6725</v>
+        <v>6742</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>855.4176902924683</v>
+        <v>1085.125659677564</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>367</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.43892391727047</v>
+        <v>67.38639720236357</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.2540699177971</v>
+        <v>33.7054368367675</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.445540674421005</v>
+        <v>4.720614138820118</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.875826053125222</v>
+        <v>0.3901265354719543</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6668</v>
+        <v>6494</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>808.1057791118044</v>
+        <v>1040.675749630003</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>47.2</v>
+        <v>69.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>72.06378636229221</v>
+        <v>70.77725256926072</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32.67948751897337</v>
+        <v>32.65009101178971</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.410577911180441</v>
+        <v>1.61985863817856</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7996298468831117</v>
+        <v>1.388794512317365</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6821</v>
+        <v>6715</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>806.1456140363823</v>
+        <v>1021.151926532133</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>471.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.97912555437939</v>
+        <v>57.06884821889251</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>24.00597240728196</v>
+        <v>21.87648195493334</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6552452231107171</v>
+        <v>1.109815324703675</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.7606882608971506</v>
+        <v>2.194384371939479</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6670</v>
+        <v>6668</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>795.7652164853163</v>
+        <v>1008.105779111804</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>287.5</v>
+        <v>47.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>59.59500957107791</v>
+        <v>72.06378637483365</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.17260630566419</v>
+        <v>32.67948754107372</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.67652164853163</v>
+        <v>3.410577911180441</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.674085566713338</v>
+        <v>0.7996298469975905</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6488</v>
+        <v>6651</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>772.2465469084318</v>
+        <v>995.5700804138802</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1110</v>
+        <v>155.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>70.73862538802064</v>
+        <v>65.78636755344894</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.50470463514266</v>
+        <v>32.06071628006673</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.554765596692569</v>
+        <v>3.316296114085121</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>19.00816712207132</v>
+        <v>-0.225883481502584</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6556</v>
+        <v>6834</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>770.0088365675093</v>
+        <v>930.6918804071923</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>73.5</v>
+        <v>101.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.27413077011651</v>
+        <v>71.71716788903925</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>43.99281948524167</v>
+        <v>45.15991508066829</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9750608080361374</v>
+        <v>0.2932753274401814</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.07769531376347601</v>
+        <v>1.408558012792776</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6651</v>
+        <v>6693</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>755.5700804138802</v>
+        <v>887.380043859049</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>155.5</v>
+        <v>215</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>65.78636755159788</v>
+        <v>73.78800992308639</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.0607162511502</v>
+        <v>43.55139436623084</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.316296114085121</v>
+        <v>0.5421636572238565</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2258834817124322</v>
+        <v>4.784345920189317</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6834</v>
+        <v>6526</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>730.6918804071923</v>
+        <v>885.8101812312409</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>101.5</v>
+        <v>696</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>71.71716790169235</v>
+        <v>57.27441593254295</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45.15991508600167</v>
+        <v>15.92800824988902</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.2932753274401814</v>
+        <v>0.8440015865291703</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.408558012201297</v>
+        <v>-1.892330284699976</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6494</v>
+        <v>6719</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>725.6757496300031</v>
+        <v>877.5354761424178</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.2</v>
+        <v>260.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.77725255581089</v>
+        <v>65.27355028331195</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>32.65009101144312</v>
+        <v>41.70842200625049</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.61985863817856</v>
+        <v>1.510745392050772</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.388794512307829</v>
+        <v>-0.1626630564506292</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6491</v>
+        <v>6531</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>722.472932803794</v>
+        <v>868.6849445445503</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>327.5</v>
+        <v>1025</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62.46959569451601</v>
+        <v>55.51986259629508</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.49264103124436</v>
+        <v>22.89687948441851</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.334735840394839</v>
+        <v>0.8567805932106699</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.768273895265472</v>
+        <v>-15.09787458754278</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6715</v>
+        <v>6770</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>711.1519265321325</v>
+        <v>823.3468390850512</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>471.5</v>
+        <v>74.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.06884822752673</v>
+        <v>55.01067941807321</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.87648196373234</v>
+        <v>22.93234185296706</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.109815324703675</v>
+        <v>0.9355652342190248</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.194384371271634</v>
+        <v>-0.927604961651192</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6548</v>
+        <v>6698</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>700.3057127685315</v>
+        <v>822.7334586354094</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>41.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.43804979973967</v>
+        <v>62.39525515005698</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45.9530305456086</v>
+        <v>32.46599330553001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.081777033083125</v>
+        <v>0.6776164700115573</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.0708441481893782</v>
+        <v>-0.2891875560227654</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6579</v>
+        <v>6517</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>699.0362223020718</v>
+        <v>814.6300515209522</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>168</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.55546649469245</v>
+        <v>69.09896481291364</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>34.39524414830597</v>
+        <v>35.63943158836702</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8753434627487922</v>
+        <v>1.56300515209522</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.242653283093481</v>
+        <v>1.552721625557503</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6690</v>
+        <v>6498</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>698.4497265344258</v>
+        <v>811.505914198876</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.54219376912556</v>
+        <v>57.36554008121749</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.17336819162572</v>
+        <v>31.50554048612483</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3776136705165085</v>
+        <v>1.99235970050026</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1603454106332229</v>
+        <v>0.3474482885282075</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6757</v>
+        <v>6691</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>689.6486036174433</v>
+        <v>811.283643862397</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>58.2</v>
+        <v>720</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>59.04976280746827</v>
+        <v>61.96953185049647</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.65353633237757</v>
+        <v>19.25466148366536</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.264860361744333</v>
+        <v>0.7988965846535838</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.304917903081402</v>
+        <v>8.869528397788958</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6592</v>
+        <v>6556</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>674.8479347788671</v>
+        <v>810.0088365675093</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>65.3</v>
+        <v>73.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.57831179002974</v>
+        <v>63.27412618652882</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.4040499608485</v>
+        <v>43.99281806072749</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6527330248616018</v>
+        <v>0.9750608080361374</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1471769404766754</v>
+        <v>0.0776953282638613</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6517</v>
+        <v>6654</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>674.6300515209522</v>
+        <v>807.5897996359054</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>217</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.09896476170455</v>
+        <v>81.47973967715242</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>35.63943154436005</v>
+        <v>49.90170831967203</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.56300515209522</v>
+        <v>2.906599723408326</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.552721625175926</v>
+        <v>4.670128404541956</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6625</v>
+        <v>6799</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>657.1316005535601</v>
+        <v>785.4627432720902</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>79.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>73.73424438267629</v>
+        <v>57.84933944051281</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.40818044517492</v>
+        <v>28.15035620443928</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8962910810064774</v>
+        <v>0.9348095912750052</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.6189978595043805</v>
+        <v>-0.7033341327412068</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6498</v>
+        <v>6642</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>656.505914198876</v>
+        <v>780.8608423077027</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>107</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.36554014288232</v>
+        <v>62.74579603884301</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.50554045720739</v>
+        <v>49.11298697147142</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.99235970050026</v>
+        <v>1.126022327329325</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3474482877650242</v>
+        <v>-0.5446593916327673</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6811</v>
+        <v>6716</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>650.2550844174391</v>
+        <v>772.1827163849222</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>230</v>
+        <v>102.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.4819618425641</v>
+        <v>57.10837420268496</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24.25791587888037</v>
+        <v>31.26407260395085</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.322590094879719</v>
+        <v>0.8949242468624757</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.239738550992115</v>
+        <v>-0.3715556015510219</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6585</v>
+        <v>6789</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>644.9557825045504</v>
+        <v>762.7374045680307</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>138</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>82.25863127841794</v>
+        <v>57.18023872367346</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>61.70627084924565</v>
+        <v>17.3033947168185</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7437366899284942</v>
+        <v>1.29207010197899</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.500090575420341</v>
+        <v>-0.5250959943303561</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6691</v>
+        <v>6548</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>641.2836438623968</v>
+        <v>740.3057127685315</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>720</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.96953184553596</v>
+        <v>61.43804979812613</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>19.25466145485838</v>
+        <v>45.953030559496</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7988965846535838</v>
+        <v>1.081777033083125</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>8.869528397312003</v>
+        <v>-0.0708441480748938</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6684</v>
+        <v>6515</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>639.5971682405229</v>
+        <v>731.7018282387438</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>50.5</v>
+        <v>9450</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.86218127160935</v>
+        <v>53.29554122068247</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.58436663073243</v>
+        <v>22.11150594718096</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8534729542142582</v>
+        <v>0.4071994871890533</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3909995503202954</v>
+        <v>129.6011827366065</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6531</v>
+        <v>6684</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>633.6849445445503</v>
+        <v>699.5971682405229</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1025</v>
+        <v>50.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.51986259135635</v>
+        <v>59.86218126243168</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.89687950891381</v>
+        <v>23.58436662278791</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8567805932106699</v>
+        <v>0.8534729542142582</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-15.09787458792434</v>
+        <v>0.3909995506446446</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6693</v>
+        <v>6579</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>627.380043859049</v>
+        <v>699.0362223020718</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>73.78800993233287</v>
+        <v>60.55546649983688</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>43.55139432066804</v>
+        <v>34.39524414084448</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5421636572238565</v>
+        <v>0.8753434627487922</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>4.784345919826809</v>
+        <v>-1.242653282998062</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6666</v>
+        <v>6756</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>621.0387890784044</v>
+        <v>678.1416604754152</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>42.95</v>
+        <v>103.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.74019656677154</v>
+        <v>58.26325622189354</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.09871651631927</v>
+        <v>27.31763444678247</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7428585176512101</v>
+        <v>1.083953984166174</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2367978612417075</v>
+        <v>-0.09348191124704019</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6645</v>
+        <v>6695</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>616.4401941659953</v>
+        <v>620.0799611997192</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15.35</v>
+        <v>58.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>67.48288244153004</v>
+        <v>59.12292877522373</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>39.75349221389747</v>
+        <v>24.32003038055074</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7440194165995356</v>
+        <v>1.019721572151448</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3401550607980371</v>
+        <v>-0.109844231272294</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6642</v>
+        <v>6683</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>605.8608423077027</v>
+        <v>606.0058917802498</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>1650</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>62.74579604645321</v>
+        <v>48.90341456428295</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>49.1129869771311</v>
+        <v>16.32088407161754</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.126022327329325</v>
+        <v>0.6568674892856573</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.5446593917854061</v>
+        <v>12.59271849583236</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6792</v>
+        <v>6510</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>600.7712409883621</v>
+        <v>604.31007612512</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>70</v>
+        <v>3610</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.6753673107805</v>
+        <v>53.7300387962411</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34.601028674203</v>
+        <v>18.32110875948803</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.87360245281469</v>
+        <v>0.4831503060205751</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.4543987266545115</v>
+        <v>36.94034840743035</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6719</v>
+        <v>6538</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>592.5354761424178</v>
+        <v>603.3839592569575</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>260.5</v>
+        <v>114.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>65.27355029937951</v>
+        <v>56.30017561572416</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>41.70842200334671</v>
+        <v>31.51030935169861</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.510745392050772</v>
+        <v>0.8466694706230615</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1626630575954113</v>
+        <v>-2.517077291107199</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6761</v>
+        <v>6792</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>587.3656834060571</v>
+        <v>600.7712409883621</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>204</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.09124751267844</v>
+        <v>56.67536726111023</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>20.3006593703996</v>
+        <v>34.60102886163532</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5660019297695537</v>
+        <v>0.87360245281469</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-2.23249500671219</v>
+        <v>-0.4543987261012165</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6505</v>
+        <v>6831</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>574.4092512225554</v>
+        <v>585.0439710914773</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>53.5</v>
+        <v>773</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.69281750287925</v>
+        <v>58.93101780721293</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12.47729341359046</v>
+        <v>24.87528833588537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.423256493801552</v>
+        <v>0.7121137770410801</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0569474052156066</v>
+        <v>-8.810974609613311</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6654</v>
+        <v>6573</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>567.5897996359054</v>
+        <v>579.9933083791716</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>217</v>
+        <v>16.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>81.47973966930809</v>
+        <v>59.64954456025955</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>49.90170830013445</v>
+        <v>13.0425818237227</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.906599723408326</v>
+        <v>0.8581207628046957</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>4.670128404274838</v>
+        <v>-0.0996000074163519</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6831</v>
+        <v>6667</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>565.0439710914773</v>
+        <v>569.812782752223</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>773</v>
+        <v>281</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.93101780749984</v>
+        <v>59.24161909272846</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.87528837545568</v>
+        <v>13.22264416449968</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7121137770410801</v>
+        <v>1.114029026806483</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-8.810974609899553</v>
+        <v>0.7889212397261094</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6782</v>
+        <v>6781</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>564.4596877983881</v>
+        <v>542.7695069055412</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>194.5</v>
+        <v>1180</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>48.09779662768553</v>
+        <v>52.45012835418107</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9.570025136894255</v>
+        <v>13.0443300530513</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.162907300207671</v>
+        <v>0.7565686046448018</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1732041166804907</v>
+        <v>1.343790575932574</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6698</v>
+        <v>6558</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>562.7334586354094</v>
+        <v>531.3039953144465</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>41.95</v>
+        <v>30.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>62.39525516502011</v>
+        <v>47.18447245255806</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32.46599333010979</v>
+        <v>25.26949497356547</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6776164700115573</v>
+        <v>0.3302023117931867</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.2891875561754067</v>
+        <v>-0.334556606445349</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6770</v>
+        <v>6658</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>543.3468390850512</v>
+        <v>516.2894879319757</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>74.2</v>
+        <v>189</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.01067941607716</v>
+        <v>53.48364210655672</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.93234186264628</v>
+        <v>32.33825353474823</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9355652342190248</v>
+        <v>1.25501231647344</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.927604961651192</v>
+        <v>-4.058730722051346</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6781</v>
+        <v>6680</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>542.7695069055412</v>
+        <v>511</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1180</v>
+        <v>51.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.45012837295499</v>
+        <v>50.91095176655806</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.04433009062974</v>
+        <v>6.863919001273827</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7565686046448018</v>
+        <v>7.533934450571676</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.343790571926119</v>
+        <v>0.9993186393016668</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6526</v>
+        <v>6570</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>540.8101812312409</v>
+        <v>496.1486317061344</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>696</v>
+        <v>54.6</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.27441594885976</v>
+        <v>52.42481175718345</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.92800824988902</v>
+        <v>23.76705450469684</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8440015865291703</v>
+        <v>0.3833070275867184</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.892330287371008</v>
+        <v>-1.109068786778863</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6605</v>
+        <v>6581</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>540.5838850128662</v>
+        <v>479.970592358576</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>141.5</v>
+        <v>109</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.46870259030582</v>
+        <v>51.89955966305028</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.39862307681944</v>
+        <v>12.11252179967143</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6278520735434507</v>
+        <v>0.3768419376858822</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.4618435742878226</v>
+        <v>-0.0665971308961273</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6716</v>
+        <v>6669</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>532.1827163849222</v>
+        <v>466.1181689692934</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>102.5</v>
+        <v>5130</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.10837416255436</v>
+        <v>50.88120539285397</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31.2640725687238</v>
+        <v>18.14533992693503</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8949242468624757</v>
+        <v>0.8772528763705716</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.371555601398382</v>
+        <v>-67.9570811290519</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6667</v>
+        <v>6679</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>509.8127827522231</v>
+        <v>453.6898377236356</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>281</v>
+        <v>285.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.24161909680485</v>
+        <v>48.85136040216892</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13.22264417726135</v>
+        <v>23.89648805720262</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.114029026806483</v>
+        <v>1.11668301656967</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.7889212394399125</v>
+        <v>-2.101179549021317</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6515</v>
+        <v>6664</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>501.6725032721083</v>
+        <v>449.3570211672675</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9450</v>
+        <v>384.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.29554122005823</v>
+        <v>43.94022319526404</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.1115059727382</v>
+        <v>25.01642423037803</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4042669905255233</v>
+        <v>0.4493816809447752</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>129.601182733172</v>
+        <v>-3.31959791684152</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6581</v>
+        <v>6597</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>479.970592358576</v>
+        <v>440.8706393226338</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>109</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.89955963880743</v>
+        <v>50.3642279826005</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.11252193338273</v>
+        <v>10.95342029530177</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3768419376858822</v>
+        <v>0.3987806652451872</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0665971308961273</v>
+        <v>-0.8235082161255737</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6789</v>
+        <v>6640</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>467.7374045680307</v>
+        <v>421.0881588648485</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>543</v>
+        <v>1120</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.18023873444282</v>
+        <v>40.2277505211943</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.30339476041768</v>
+        <v>26.20414624338033</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.29207010197899</v>
+        <v>0.6745921331383645</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.5250959955705117</v>
+        <v>-5.844428668762077</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6669</v>
+        <v>6776</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>466.1181689692934</v>
+        <v>413.0446299831584</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>5130</v>
+        <v>59.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.88120540807952</v>
+        <v>49.98653859611562</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.14533994843062</v>
+        <v>9.190569822775885</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8772528763705716</v>
+        <v>0.7364648797195718</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-67.95708113668366</v>
+        <v>-0.1373214024441919</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6799</v>
+        <v>6588</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>465.4627432720901</v>
+        <v>407.8954663890353</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>107.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>57.84933943339352</v>
+        <v>42.35619710147279</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.15035606384992</v>
+        <v>16.27212687535586</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9348095912750052</v>
+        <v>0.4403768233267193</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.7033341327412068</v>
+        <v>0.6431512648268365</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6570</v>
+        <v>6805</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>456.1486317061344</v>
+        <v>398.7284014102837</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>54.6</v>
+        <v>1755</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.42481174379403</v>
+        <v>44.56001974637073</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.7670544738388</v>
+        <v>14.95563451346673</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3833070275867184</v>
+        <v>0.4235421821256706</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.109068786912422</v>
+        <v>-22.32059347337242</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6606</v>
+        <v>6584</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>453.1834028491537</v>
+        <v>392.2995944331854</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>25</v>
+        <v>625</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.63931545955293</v>
+        <v>47.24033082115122</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.34269588008988</v>
+        <v>11.99895627351633</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5136885673212114</v>
+        <v>0.4166067427830628</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1757053266517322</v>
+        <v>-4.897651497646235</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6788</v>
+        <v>6720</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>451.7351938186157</v>
+        <v>367.5597018916417</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>438</v>
+        <v>142</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.62888251153285</v>
+        <v>31.40520770213884</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9.543018903340466</v>
+        <v>32.37499213641874</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5844490702982315</v>
+        <v>0.4962433826211615</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.191966050903875</v>
+        <v>-0.4338529336626631</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6510</v>
+        <v>6560</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>449.3018419501886</v>
+        <v>365.8166742834656</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>3610</v>
+        <v>38</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.73003882867828</v>
+        <v>48.66411407423659</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.32110886987913</v>
+        <v>13.89738325434931</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4826123894921555</v>
+        <v>0.4769321523662099</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>36.94034839521942</v>
+        <v>-0.1219414082608044</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6756</v>
+        <v>6532</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>443.1416604754152</v>
+        <v>357.8915831923025</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>103.5</v>
+        <v>91.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>58.26325621789066</v>
+        <v>46.09019394034403</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.31763444006683</v>
+        <v>22.77687482106036</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.083953984166174</v>
+        <v>0.4693127005229541</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0934819114759915</v>
+        <v>-0.9849691377950304</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6597</v>
+        <v>6512</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>440.8706393226338</v>
+        <v>350.8206024752992</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.3642279826005</v>
+        <v>51.80891999353064</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10.95342015644783</v>
+        <v>9.097562983992548</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3987806652451872</v>
+        <v>0.5410566937326722</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.8235082165071532</v>
+        <v>-0.3545710958930965</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6538</v>
+        <v>6771</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>433.3839592569574</v>
+        <v>344.8325442287269</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>114.5</v>
+        <v>42</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>56.30017561894817</v>
+        <v>46.22371642440847</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>31.51030932301752</v>
+        <v>14.02746498428115</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8466694706230615</v>
+        <v>2.296825479077181</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.5170772913743</v>
+        <v>0.0948303683630313</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6598</v>
+        <v>6743</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>433.26031050972</v>
+        <v>338.3828257707834</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.15</v>
+        <v>29</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.21932073037649</v>
+        <v>49.50494794959324</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.98196289379477</v>
+        <v>19.60396743861664</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.730679224304985</v>
+        <v>0.4233598211674846</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0973850437636098</v>
+        <v>-0.2274145851520772</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6790</v>
+        <v>6692</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>431.9082624105885</v>
+        <v>337.5501471522792</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>40.05</v>
+        <v>27</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>57.81957106909656</v>
+        <v>48.54069699700314</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.69084872186259</v>
+        <v>22.41233210320248</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8015968810667898</v>
+        <v>1.334770468634914</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0718207477919393</v>
+        <v>0.2841797902961656</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6753</v>
+        <v>6708</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>419.3162582510543</v>
+        <v>331.1617641552466</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>121.5</v>
+        <v>39.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.88071840611747</v>
+        <v>47.69413375504143</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.17853104138907</v>
+        <v>15.1933117230612</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5277531797640241</v>
+        <v>0.513416997832753</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.09138291642094119</v>
+        <v>-0.0563190215787685</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6658</v>
+        <v>6643</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>416.2894879319757</v>
+        <v>326.7879391794831</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>189</v>
+        <v>494</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.48364210114089</v>
+        <v>40.73448371625519</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32.33825345894309</v>
+        <v>26.40102873469428</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.25501231647344</v>
+        <v>0.598897058187882</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-4.058730722547423</v>
+        <v>-6.037609793522932</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6776</v>
+        <v>6806</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>413.0446299831584</v>
+        <v>321.1806280133556</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>59.3</v>
+        <v>3.24</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.98653864136385</v>
+        <v>30.30810162010731</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>9.190569815807718</v>
+        <v>32.28363367198867</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7364648797195718</v>
+        <v>1.437623507568395</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1373214025968265</v>
+        <v>0.3767060656906009</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6558</v>
+        <v>6706</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>411.3039953144464</v>
+        <v>319.8451855910437</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>30.9</v>
+        <v>172</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.18447244295042</v>
+        <v>48.69595574494014</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.26949496125644</v>
+        <v>18.33759879254464</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3302023117931867</v>
+        <v>0.4565582620914242</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3345566063785734</v>
+        <v>-3.936865684636677</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6695</v>
+        <v>6546</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>410.0799611997192</v>
+        <v>312.9547032703164</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>58.4</v>
+        <v>75</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>59.12292879005234</v>
+        <v>50.17604797029433</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.32003042524866</v>
+        <v>18.79833936336457</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.019721572151448</v>
+        <v>0.305171469891753</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1098442316061849</v>
+        <v>-0.7872609560339345</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6589</v>
+        <v>6641</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>408.1947952185165</v>
+        <v>307.3953855107001</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>46.45</v>
+        <v>18.35</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.45511546880292</v>
+        <v>48.33883550074246</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.01787436469437</v>
+        <v>18.47475541857973</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8033679113291566</v>
+        <v>1.295478810426599</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.4661562880891495</v>
+        <v>0.010076981174512</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6512</v>
+        <v>6561</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>380.8206024752992</v>
+        <v>301.597941943676</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>19.5</v>
+        <v>338</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.80891998223631</v>
+        <v>39.95310179169165</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.097563117431704</v>
+        <v>15.92831024669716</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5410566937326722</v>
+        <v>0.7831290660455803</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.3545710958740165</v>
+        <v>-2.415889121095163</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6754</v>
+        <v>6591</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>373.0387850329988</v>
+        <v>297.5295297100117</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>45.5</v>
+        <v>55.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>54.45692312627976</v>
+        <v>47.89571698016637</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.95425977790755</v>
+        <v>21.27229468791863</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4981974628195325</v>
+        <v>0.3419286435501053</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.086599771409029</v>
+        <v>-0.1213228753602536</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6840</v>
+        <v>6568</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>365.4206114395907</v>
+        <v>280.2611788583437</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>176.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.69828557839744</v>
+        <v>36.49207691973459</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.51785083423705</v>
+        <v>26.79358854175573</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.379633914857369</v>
+        <v>0.3773273955494983</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1156446524697103</v>
+        <v>-2.716731307425485</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6614</v>
+        <v>6530</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>358.1206578860162</v>
+        <v>273.3349459004269</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>40.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.09392008905739</v>
+        <v>43.42085234701366</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.43856064303491</v>
+        <v>15.37030248505064</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.261678801881495</v>
+        <v>0.5481834479056017</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2100880551975733</v>
+        <v>-1.258141815888457</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6573</v>
+        <v>6624</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>354.9933083791717</v>
+        <v>264.4797919522783</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>16.2</v>
+        <v>42.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>59.64954455309401</v>
+        <v>50.84351011611045</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.04258185214769</v>
+        <v>12.87641141601794</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8581207628046957</v>
+        <v>0.1660141506019486</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.09960000742588999</v>
+        <v>-0.8466583947305986</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6720</v>
+        <v>6689</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>347.5597018916417</v>
+        <v>263.0097790658329</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>31.40520779388784</v>
+        <v>43.94801996005704</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>32.37499212788278</v>
+        <v>13.15457280986532</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4962433826211615</v>
+        <v>0.6604450680510734</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4338529362383925</v>
+        <v>-0.2673178463243377</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6771</v>
+        <v>6533</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>344.8325442287269</v>
+        <v>237.9493716166865</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>42</v>
+        <v>201.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.22371699977454</v>
+        <v>41.54824106436801</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.02746480908678</v>
+        <v>17.38626703298286</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.296825479077181</v>
+        <v>0.3659666306626591</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0948303679432899</v>
+        <v>-1.991817398688603</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6743</v>
+        <v>6486</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>338.3828257707834</v>
+        <v>219.7196600537474</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>29</v>
+        <v>81.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.50494793456892</v>
+        <v>44.91010668425125</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.60396749008454</v>
+        <v>17.18046689721345</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4233598211674846</v>
+        <v>0.4919923609059986</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2274145852283952</v>
+        <v>0.1066056059074328</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6640</v>
+        <v>6552</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>336.0881588648486</v>
+        <v>193.1053949052276</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1120</v>
+        <v>31.05</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.22775053126631</v>
+        <v>50.2543622094521</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>26.20414625560005</v>
+        <v>16.06653903305078</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6745921331383645</v>
+        <v>0.5920959602831702</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.844428670956432</v>
+        <v>-0.3735132207745319</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6561</v>
+        <v>6577</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>331.5979419436761</v>
+        <v>184.5927133941264</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>338</v>
+        <v>75.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.95310169300311</v>
+        <v>32.22666725827857</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.92831024669716</v>
+        <v>14.44189594914305</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7831290660455803</v>
+        <v>1.359271339412637</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.415889122239982</v>
+        <v>-0.5273502491747291</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6560</v>
+        <v>6722</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>325.8166742834656</v>
+        <v>175.2247126256183</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>38</v>
+        <v>37.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.66411442720144</v>
+        <v>40.84784003316734</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.89738334483611</v>
+        <v>15.11452675435338</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4769321523662099</v>
+        <v>0.3261680613668061</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1219414088522674</v>
+        <v>-0.1130206901409136</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6732</v>
+        <v>6835</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>325.7168232961237</v>
+        <v>160.2019229840527</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>165.5</v>
+        <v>36.55</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.62164091442502</v>
+        <v>42.5552187182104</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.33337246645867</v>
+        <v>13.96652691060163</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7532263202092644</v>
+        <v>0.1401610274202643</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.02323621103567</v>
+        <v>-0.1441846346349169</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, adx_trending, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6805</v>
+        <v>6674</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>323.7284014102829</v>
+        <v>155.3178938175574</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1755</v>
+        <v>17.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.56001977564354</v>
+        <v>45.9465259515588</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.95563459842022</v>
+        <v>17.1776694624163</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4235421821256706</v>
+        <v>0.6990016188308878</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,2500 +4651,9 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-22.32059348109954</v>
+        <v>-0.0056636724478135</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>6582</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>申豐</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>322.428039266248</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>51.70125709801454</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>24.05578276935505</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>0.8574275770932969</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>0.035724738492077</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>6806</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>森崴能源</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>321.1806280133556</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>30.30810167316417</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>32.28363363632754</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>1.437623507568395</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>0.3767060654616472</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>6706</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>惠特</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>319.7777602963761</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>48.69595573196401</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>18.33759883596144</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0.452274617221893</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-3.936865684961013</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>6763</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>綠界科技</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>314.2172627049661</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>52.94582144949013</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>23.49084955731175</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.3818612101319157</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>0.1566599524950672</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>6823</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>濾能</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>311.8975746106038</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>50.71449686716197</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>23.92400665246222</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>1.307968081718171</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>0.07118777019872349</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>6568</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>宏觀</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>310.2611788583437</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>36.49207688951501</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>26.79358855192561</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0.3773273955494983</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-2.716731307921549</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>6641</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>基士德-KY</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>307.3953855107001</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>48.33883527813204</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>18.47475540330496</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>1.295478810426599</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>0.0100769811935904</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>6679</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>鈺太</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>298.6898377236355</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>285.5</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>48.85136045430271</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>23.89648809888316</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>1.11668301656967</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-2.101179550833836</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>6532</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>瑞耘</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>297.8915831923025</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>46.09019397502704</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>22.77687480351931</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.4693127005229541</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>-0.984969138100301</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>6591</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>動力-KY</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>297.5295297100116</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>47.89571703494248</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>21.27229460215298</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>0.3419286435501053</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>-0.1213228756369064</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>6727</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>亞泰金屬</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>293.4645960592337</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>449</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>47.52615106155954</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>20.89367940726599</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0.6727984200975592</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>-13.08914703603625</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>6794</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>向榮生技-創</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>292.1953224228291</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>43.80472455370605</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>12.3421806971738</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.9018978853386032</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-0.2441823158338045</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>6683</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>雍智科技</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>291.0058917802497</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>1650</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>48.90341456772728</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>16.32088411938042</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.6568674892856573</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>12.59271849487851</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>6735</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>美達科技</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>289.1684870095842</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>43.6473054695755</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>17.0988044923632</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.5440638629536038</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>-1.217928507438332</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>6655</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>科定</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>286.3466308157641</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>41.56732392781632</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>11.3868091341395</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0.4530174904144125</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>-0.1615298824308073</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>6803</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>崑鼎</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>280.7227010509254</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>286.5</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>46.15617837089619</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>24.93383606611805</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.3365510385601423</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>0.0200492280902971</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>6657</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>華安</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>279.5474175138404</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>44.08976689723436</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>20.73155710423782</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.3089016272550021</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>0.0327490752107852</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>6546</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>正基</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>272.9547032703164</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>50.17604804222429</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>18.7983392465595</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0.305171469891753</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>-0.7872609567017088</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>6689</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>伊雲谷</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>263.0097790658329</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>43.94801984213267</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>13.15457281310805</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.6604450680510734</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-0.2673178466296059</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>6550</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>北極星藥業-KY</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>257.9491049682562</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>39.19949771631654</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>34.80211483433269</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0.7151758191876006</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>0.1882558759792705</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>6680</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>鑫創電子</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>50.91095202681439</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>6.863919013998276</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>7.533934450571676</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0.999318639187194</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, volume_break, market_above_ma60, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>6486</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>互動</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>249.7196600537474</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>44.91010659310117</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>17.18046690370282</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0.4919923609059986</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0.1066056056975665</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>6643</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>241.787939179483</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>494</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>40.73448376253424</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>26.40102871365261</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>0.598897058187882</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-6.037609797338803</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>6739</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>239.4957356391686</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>40.01878434124902</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>13.15636391269744</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.4617560143540447</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>-7.963280099140285</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>6664</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>群翊</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>239.3570211672675</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>43.94022317849431</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>25.01642428573938</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.4493816809447752</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-3.319597917032329</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>6533</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>237.9119115071911</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>41.54824103719996</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>17.38626706235569</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>0.3622206197131217</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-1.991817399165584</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>6768</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>志強-KY</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>236.0692268231926</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>42.65018498822675</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>19.68857497184664</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.439277772592053</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>-0.9863750521226752</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>6741</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>91APP*-KY</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>234.5386283811026</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>47.2321049815418</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>11.56697742983538</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.3088788572932415</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>-0.2008244014555686</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>6588</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>東典光電</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>232.8954663890353</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>42.35619707533778</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>16.2721268829133</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.4403768233267193</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>0.643151264817301</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>6829</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>千附精密</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>232.7777222211289</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>48.70296764096494</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>15.22480616529756</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>0.8228802885376895</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>-1.221840132364091</v>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>6534</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>正瀚-創</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>231.5122781301536</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>51.45026575338206</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>15.52807094804064</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0.2043133024836616</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>0.2146645791527284</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>6624</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>萬年清</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>224.4797919522783</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>50.84351027353544</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>12.87641161339414</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>0.1660141506019486</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>-0.8466584010268163</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>6708</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>天擎</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>221.1617641552466</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>47.69413391983097</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>15.19331177555679</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>0.513416997832753</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-0.0563190217600273</v>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>6530</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>創威</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>213.3349459004269</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>43.42085244270847</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>15.37030252938232</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.5481834479056017</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>-1.258141816842424</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>6584</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>212.2995944331853</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>625</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>47.24033081499794</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>11.99895625449434</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0.4166067427830628</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>-4.897651498123146</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>6796</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>晉弘</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>210.6015728729433</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>40.60646692273533</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>30.94907525177072</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>0.5849974715911801</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>0.2971462308241057</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>6692</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>進能服</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>202.5501471522793</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>48.5406969700626</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>22.41233210779917</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>1.334770468634914</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>0.2841797902866259</v>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>6552</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>易華電</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>193.1053949052276</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>50.25436222347735</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>16.06653902011597</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.5920959602831702</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>-0.3735132209367104</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>6504</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>南六</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>189.5613741545583</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>38.29897699320191</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>19.12552839171002</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0.6915485751808468</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>0.0817778242437419</v>
-      </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>6577</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>勁豐</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>184.5927133941264</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>32.22666725827857</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>14.4418959555255</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>1.359271339412637</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-0.5273502493846172</v>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>6807</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>峰源-KY</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>176.0560341964963</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>33.65</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>44.56133149159712</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>25.25670996278497</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0.5815075318441455</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>0.1995401501344236</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>6722</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>輝創</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>175.2247126256183</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>40.84784527408016</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>15.11452321942032</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>0.3261680613668061</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>-0.1130206995852425</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>6835</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>圓裕</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>160.2019229840527</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>42.55521877088504</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>13.96652687595332</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.1401610274202643</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>-0.1441846347112411</v>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>6671</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>三能-KY</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>154.1282557155093</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>31.28109325896793</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>16.53314461321896</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>1.13869551264866</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>0.0615953555021595</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>6838</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>台新藥</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>146.995683722349</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>36.34457183352947</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>9.987312232911378</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.8223454801759448</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>0.0562771370931587</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>6541</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>泰福-KY</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>145.3276399708073</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>52.23109413513934</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>15.0547949184836</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.7868236035429527</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>0.0409418607723668</v>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>6674</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>鋐寶科技</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>135.3178938175575</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>45.94652571266353</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>17.17766948296974</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>0.6990016188308878</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>-0.0056636725050527</v>
-      </c>
-      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6570</v>
+        <v>6727</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>496.1486317061344</v>
+        <v>503.4645960592337</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>54.6</v>
+        <v>449</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.42481175718345</v>
+        <v>47.52615106428384</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.76705450469684</v>
+        <v>20.89367945259401</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3833070275867184</v>
+        <v>0.6727984200975592</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.109068786778863</v>
+        <v>-13.08914703597903</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6581</v>
+        <v>6570</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>479.970592358576</v>
+        <v>496.1486317061344</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109</v>
+        <v>54.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.89955966305028</v>
+        <v>52.42481175718345</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.11252179967143</v>
+        <v>23.76705450469684</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3768419376858822</v>
+        <v>0.3833070275867184</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0665971308961273</v>
+        <v>-1.109068786778863</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6669</v>
+        <v>6581</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>466.1181689692934</v>
+        <v>479.970592358576</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>5130</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.88120539285397</v>
+        <v>51.89955966305028</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.14533992693503</v>
+        <v>12.11252179967143</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8772528763705716</v>
+        <v>0.3768419376858822</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-67.9570811290519</v>
+        <v>-0.0665971308961273</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6679</v>
+        <v>6669</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>453.6898377236356</v>
+        <v>466.1181689692934</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>285.5</v>
+        <v>5130</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.85136040216892</v>
+        <v>50.88120539285397</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.89648805720262</v>
+        <v>18.14533992693503</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.11668301656967</v>
+        <v>0.8772528763705716</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.101179549021317</v>
+        <v>-67.9570811290519</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6664</v>
+        <v>6679</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>449.3570211672675</v>
+        <v>453.6898377236356</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>384.5</v>
+        <v>285.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.94022319526404</v>
+        <v>48.85136040216892</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.01642423037803</v>
+        <v>23.89648805720262</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4493816809447752</v>
+        <v>1.11668301656967</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-3.31959791684152</v>
+        <v>-2.101179549021317</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6597</v>
+        <v>6664</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>440.8706393226338</v>
+        <v>449.3570211672675</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>384.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.3642279826005</v>
+        <v>43.94022319526404</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.95342029530177</v>
+        <v>25.01642423037803</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3987806652451872</v>
+        <v>0.4493816809447752</v>
       </c>
       <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.8235082161255737</v>
+        <v>-3.31959791684152</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6640</v>
+        <v>6597</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>421.0881588648485</v>
+        <v>440.8706393226338</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1120</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.2277505211943</v>
+        <v>50.3642279826005</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.20414624338033</v>
+        <v>10.95342029530177</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6745921331383645</v>
+        <v>0.3987806652451872</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-5.844428668762077</v>
+        <v>-0.8235082161255737</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6776</v>
+        <v>6640</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>413.0446299831584</v>
+        <v>421.0881588648485</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>59.3</v>
+        <v>1120</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.98653859611562</v>
+        <v>40.2277505211943</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.190569822775885</v>
+        <v>26.20414624338033</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7364648797195718</v>
+        <v>0.6745921331383645</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1373214024441919</v>
+        <v>-5.844428668762077</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6588</v>
+        <v>6776</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>407.8954663890353</v>
+        <v>413.0446299831584</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.5</v>
+        <v>59.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>42.35619710147279</v>
+        <v>49.98653859611562</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.27212687535586</v>
+        <v>9.190569822775885</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4403768233267193</v>
+        <v>0.7364648797195718</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6431512648268365</v>
+        <v>-0.1373214024441919</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6805</v>
+        <v>6588</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>398.7284014102837</v>
+        <v>407.8954663890353</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1755</v>
+        <v>107.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.56001974637073</v>
+        <v>42.35619710147279</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.95563451346673</v>
+        <v>16.27212687535586</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4235421821256706</v>
+        <v>0.4403768233267193</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-22.32059347337242</v>
+        <v>0.6431512648268365</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6584</v>
+        <v>6805</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>392.2995944331854</v>
+        <v>398.7284014102837</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>625</v>
+        <v>1755</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.24033082115122</v>
+        <v>44.56001974637073</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.99895627351633</v>
+        <v>14.95563451346673</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4166067427830628</v>
+        <v>0.4235421821256706</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-4.897651497646235</v>
+        <v>-22.32059347337242</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6720</v>
+        <v>6584</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>367.5597018916417</v>
+        <v>392.2995944331854</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>142</v>
+        <v>625</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>31.40520770213884</v>
+        <v>47.24033082115122</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>32.37499213641874</v>
+        <v>11.99895627351633</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4962433826211615</v>
+        <v>0.4166067427830628</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.4338529336626631</v>
+        <v>-4.897651497646235</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6560</v>
+        <v>6720</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>365.8166742834656</v>
+        <v>367.5597018916417</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.66411407423659</v>
+        <v>31.40520770213884</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.89738325434931</v>
+        <v>32.37499213641874</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4769321523662099</v>
+        <v>0.4962433826211615</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>2</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1219414082608044</v>
+        <v>-0.4338529336626631</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6532</v>
+        <v>6560</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>357.8915831923025</v>
+        <v>365.8166742834656</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>91.2</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.09019394034403</v>
+        <v>48.66411407423659</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.77687482106036</v>
+        <v>13.89738325434931</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4693127005229541</v>
+        <v>0.4769321523662099</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>2</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.9849691377950304</v>
+        <v>-0.1219414082608044</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6512</v>
+        <v>6532</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>350.8206024752992</v>
+        <v>357.8915831923025</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>19.5</v>
+        <v>91.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.80891999353064</v>
+        <v>46.09019394034403</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>9.097562983992548</v>
+        <v>22.77687482106036</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5410566937326722</v>
+        <v>0.4693127005229541</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.3545710958930965</v>
+        <v>-0.9849691377950304</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6771</v>
+        <v>6512</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>344.8325442287269</v>
+        <v>350.8206024752992</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>42</v>
+        <v>19.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.22371642440847</v>
+        <v>51.80891999353064</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.02746498428115</v>
+        <v>9.097562983992548</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.296825479077181</v>
+        <v>0.5410566937326722</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0948303683630313</v>
+        <v>-0.3545710958930965</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6743</v>
+        <v>6771</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>338.3828257707834</v>
+        <v>344.8325442287269</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>49.50494794959324</v>
+        <v>46.22371642440847</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.60396743861664</v>
+        <v>14.02746498428115</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4233598211674846</v>
+        <v>2.296825479077181</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2274145851520772</v>
+        <v>0.0948303683630313</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6692</v>
+        <v>6743</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>337.5501471522792</v>
+        <v>338.3828257707834</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.54069699700314</v>
+        <v>49.50494794959324</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.41233210320248</v>
+        <v>19.60396743861664</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.334770468634914</v>
+        <v>0.4233598211674846</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2841797902961656</v>
+        <v>-0.2274145851520772</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6708</v>
+        <v>6692</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>331.1617641552466</v>
+        <v>337.5501471522792</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>39.8</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.69413375504143</v>
+        <v>48.54069699700314</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.1933117230612</v>
+        <v>22.41233210320248</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.513416997832753</v>
+        <v>1.334770468634914</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0563190215787685</v>
+        <v>0.2841797902961656</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6643</v>
+        <v>6708</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>326.7879391794831</v>
+        <v>331.1617641552466</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>494</v>
+        <v>39.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.73448371625519</v>
+        <v>47.69413375504143</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>26.40102873469428</v>
+        <v>15.1933117230612</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.598897058187882</v>
+        <v>0.513416997832753</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-6.037609793522932</v>
+        <v>-0.0563190215787685</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6806</v>
+        <v>6643</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>321.1806280133556</v>
+        <v>326.7879391794831</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>3.24</v>
+        <v>494</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>30.30810162010731</v>
+        <v>40.73448371625519</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>32.28363367198867</v>
+        <v>26.40102873469428</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.437623507568395</v>
+        <v>0.598897058187882</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3767060656906009</v>
+        <v>-6.037609793522932</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6706</v>
+        <v>6806</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>319.8451855910437</v>
+        <v>321.1806280133556</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>172</v>
+        <v>3.24</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.69595574494014</v>
+        <v>30.30810162010731</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.33759879254464</v>
+        <v>32.28363367198867</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4565582620914242</v>
+        <v>1.437623507568395</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-3.936865684636677</v>
+        <v>0.3767060656906009</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6546</v>
+        <v>6706</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>312.9547032703164</v>
+        <v>319.8451855910437</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.17604797029433</v>
+        <v>48.69595574494014</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.79833936336457</v>
+        <v>18.33759879254464</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.305171469891753</v>
+        <v>0.4565582620914242</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.7872609560339345</v>
+        <v>-3.936865684636677</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6641</v>
+        <v>6546</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>307.3953855107001</v>
+        <v>312.9547032703164</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>18.35</v>
+        <v>75</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.33883550074246</v>
+        <v>50.17604797029433</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.47475541857973</v>
+        <v>18.79833936336457</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.295478810426599</v>
+        <v>0.305171469891753</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.010076981174512</v>
+        <v>-0.7872609560339345</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6561</v>
+        <v>6641</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>301.597941943676</v>
+        <v>307.3953855107001</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>338</v>
+        <v>18.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.95310179169165</v>
+        <v>48.33883550074246</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.92831024669716</v>
+        <v>18.47475541857973</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7831290660455803</v>
+        <v>1.295478810426599</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.415889121095163</v>
+        <v>0.010076981174512</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6591</v>
+        <v>6561</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>297.5295297100117</v>
+        <v>301.597941943676</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>55.5</v>
+        <v>338</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.89571698016637</v>
+        <v>39.95310179169165</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.27229468791863</v>
+        <v>15.92831024669716</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3419286435501053</v>
+        <v>0.7831290660455803</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1213228753602536</v>
+        <v>-2.415889121095163</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6568</v>
+        <v>6591</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>280.2611788583437</v>
+        <v>297.5295297100117</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>176.5</v>
+        <v>55.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>36.49207691973459</v>
+        <v>47.89571698016637</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.79358854175573</v>
+        <v>21.27229468791863</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3773273955494983</v>
+        <v>0.3419286435501053</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-2.716731307425485</v>
+        <v>-0.1213228753602536</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6530</v>
+        <v>6568</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>273.3349459004269</v>
+        <v>280.2611788583437</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>176.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.42085234701366</v>
+        <v>36.49207691973459</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.37030248505064</v>
+        <v>26.79358854175573</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5481834479056017</v>
+        <v>0.3773273955494983</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.258141815888457</v>
+        <v>-2.716731307425485</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6624</v>
+        <v>6530</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>264.4797919522783</v>
+        <v>273.3349459004269</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>42.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.84351011611045</v>
+        <v>43.42085234701366</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12.87641141601794</v>
+        <v>15.37030248505064</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1660141506019486</v>
+        <v>0.5481834479056017</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.8466583947305986</v>
+        <v>-1.258141815888457</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6689</v>
+        <v>6624</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>263.0097790658329</v>
+        <v>264.4797919522783</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>67</v>
+        <v>42.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.94801996005704</v>
+        <v>50.84351011611045</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.15457280986532</v>
+        <v>12.87641141601794</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6604450680510734</v>
+        <v>0.1660141506019486</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2673178463243377</v>
+        <v>-0.8466583947305986</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6533</v>
+        <v>6689</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>237.9493716166865</v>
+        <v>263.0097790658329</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>201.5</v>
+        <v>67</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.54824106436801</v>
+        <v>43.94801996005704</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.38626703298286</v>
+        <v>13.15457280986532</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3659666306626591</v>
+        <v>0.6604450680510734</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.991817398688603</v>
+        <v>-0.2673178463243377</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6486</v>
+        <v>6533</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>219.7196600537474</v>
+        <v>237.9493716166865</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>81.8</v>
+        <v>201.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.91010668425125</v>
+        <v>41.54824106436801</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.18046689721345</v>
+        <v>17.38626703298286</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4919923609059986</v>
+        <v>0.3659666306626591</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1066056059074328</v>
+        <v>-1.991817398688603</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6552</v>
+        <v>6486</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>193.1053949052276</v>
+        <v>219.7196600537474</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>31.05</v>
+        <v>81.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.2543622094521</v>
+        <v>44.91010668425125</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.06653903305078</v>
+        <v>17.18046689721345</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5920959602831702</v>
+        <v>0.4919923609059986</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.3735132207745319</v>
+        <v>0.1066056059074328</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6577</v>
+        <v>6552</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>184.5927133941264</v>
+        <v>193.1053949052276</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>75.7</v>
+        <v>31.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>32.22666725827857</v>
+        <v>50.2543622094521</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.44189594914305</v>
+        <v>16.06653903305078</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.359271339412637</v>
+        <v>0.5920959602831702</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5273502491747291</v>
+        <v>-0.3735132207745319</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6722</v>
+        <v>6577</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>175.2247126256183</v>
+        <v>184.5927133941264</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>37.4</v>
+        <v>75.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>40.84784003316734</v>
+        <v>32.22666725827857</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.11452675435338</v>
+        <v>14.44189594914305</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3261680613668061</v>
+        <v>1.359271339412637</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1130206901409136</v>
+        <v>-0.5273502491747291</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6835</v>
+        <v>6722</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>160.2019229840527</v>
+        <v>175.2247126256183</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>36.55</v>
+        <v>37.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.5552187182104</v>
+        <v>40.84784003316734</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.96652691060163</v>
+        <v>15.11452675435338</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1401610274202643</v>
+        <v>0.3261680613668061</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,62 +4598,115 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1441846346349169</v>
+        <v>-0.1130206901409136</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>圓裕</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>160.2019229840527</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>42.5552187182104</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>13.96652691060163</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.1401610274202643</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.1441846346349169</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
         <v>6674</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>鋐寶科技</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D79" s="2" t="n">
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
         <v>155.3178938175574</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E80" s="2" t="n">
         <v>17.45</v>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>45.9465259515588</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>17.1776694624163</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J80" s="2" t="n">
         <v>0.6990016188308878</v>
       </c>
-      <c r="K79" s="2" t="n">
+      <c r="K80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" s="2" t="n">
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
         <v>-0.0056636724478135</v>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-18.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6693</v>
+        <v>6670</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>887.380043859049</v>
+        <v>910.7652164853164</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>215</v>
+        <v>287.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>73.78800992308639</v>
+        <v>59.59500954264795</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>43.55139436623084</v>
+        <v>33.17260645618079</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5421636572238565</v>
+        <v>1.67652164853163</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4.784345920189317</v>
+        <v>1.674085568335069</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6526</v>
+        <v>6693</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>885.8101812312409</v>
+        <v>887.380043859049</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>696</v>
+        <v>215</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.27441593254295</v>
+        <v>73.78800992308639</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.92800824988902</v>
+        <v>43.55139436623084</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8440015865291703</v>
+        <v>0.5421636572238565</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.892330284699976</v>
+        <v>4.784345920189317</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6719</v>
+        <v>6526</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>877.5354761424178</v>
+        <v>885.8101812312409</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>260.5</v>
+        <v>696</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.27355028331195</v>
+        <v>57.27441593254295</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41.70842200625049</v>
+        <v>15.92800824988902</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.510745392050772</v>
+        <v>0.8440015865291703</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.1626630564506292</v>
+        <v>-1.892330284699976</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6531</v>
+        <v>6719</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>868.6849445445503</v>
+        <v>877.5354761424178</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1025</v>
+        <v>260.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.51986259629508</v>
+        <v>65.27355028331195</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.89687948441851</v>
+        <v>41.70842200625049</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8567805932106699</v>
+        <v>1.510745392050772</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-15.09787458754278</v>
+        <v>-0.1626630564506292</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6770</v>
+        <v>6531</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>823.3468390850512</v>
+        <v>868.6849445445503</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>74.2</v>
+        <v>1025</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.01067941807321</v>
+        <v>55.51986259629508</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.93234185296706</v>
+        <v>22.89687948441851</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.9355652342190248</v>
+        <v>0.8567805932106699</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.927604961651192</v>
+        <v>-15.09787458754278</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6698</v>
+        <v>6821</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>822.7334586354094</v>
+        <v>866.1456140363823</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41.95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.39525515005698</v>
+        <v>56.97912554273852</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.46599330553001</v>
+        <v>24.00597229021887</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6776164700115573</v>
+        <v>0.6552452231107171</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.2891875560227654</v>
+        <v>-0.7606882606968148</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6517</v>
+        <v>6491</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>814.6300515209522</v>
+        <v>842.472932803794</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>327.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.09896481291364</v>
+        <v>62.46959566109601</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35.63943158836702</v>
+        <v>27.49264103124435</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.56300515209522</v>
+        <v>1.334735840394839</v>
       </c>
       <c r="K17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.552721625557503</v>
+        <v>-1.7682738945023</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6498</v>
+        <v>6645</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>811.505914198876</v>
+        <v>836.4401941659953</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>107</v>
+        <v>15.35</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.36554008121749</v>
+        <v>67.48288221737064</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.50554048612483</v>
+        <v>39.75349252258958</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.99235970050026</v>
+        <v>0.7440194165995356</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3474482885282075</v>
+        <v>0.3401550610842302</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6691</v>
+        <v>6770</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>811.283643862397</v>
+        <v>823.3468390850512</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>720</v>
+        <v>74.2</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.96953185049647</v>
+        <v>55.01067941807321</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.25466148366536</v>
+        <v>22.93234185296706</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7988965846535838</v>
+        <v>0.9355652342190248</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>8.869528397788958</v>
+        <v>-0.927604961651192</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6556</v>
+        <v>6698</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>810.0088365675093</v>
+        <v>822.7334586354094</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>73.5</v>
+        <v>41.95</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.27412618652882</v>
+        <v>62.39525515005698</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>43.99281806072749</v>
+        <v>32.46599330553001</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9750608080361374</v>
+        <v>0.6776164700115573</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0776953282638613</v>
+        <v>-0.2891875560227654</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6654</v>
+        <v>6517</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>807.5897996359054</v>
+        <v>814.6300515209522</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>217</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>81.47973967715242</v>
+        <v>69.09896481291364</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>49.90170831967203</v>
+        <v>35.63943158836702</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.906599723408326</v>
+        <v>1.56300515209522</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.670128404541956</v>
+        <v>1.552721625557503</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6799</v>
+        <v>6498</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>785.4627432720902</v>
+        <v>811.505914198876</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>107</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.84933944051281</v>
+        <v>57.36554008121749</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.15035620443928</v>
+        <v>31.50554048612483</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9348095912750052</v>
+        <v>1.99235970050026</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.7033341327412068</v>
+        <v>0.3474482885282075</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6642</v>
+        <v>6691</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>780.8608423077027</v>
+        <v>811.283643862397</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>720</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.74579603884301</v>
+        <v>61.96953185049647</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>49.11298697147142</v>
+        <v>19.25466148366536</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.126022327329325</v>
+        <v>0.7988965846535838</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.5446593916327673</v>
+        <v>8.869528397788958</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6716</v>
+        <v>6556</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>772.1827163849222</v>
+        <v>810.0088365675093</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>102.5</v>
+        <v>73.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.10837420268496</v>
+        <v>63.27412618652882</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.26407260395085</v>
+        <v>43.99281806072749</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8949242468624757</v>
+        <v>0.9750608080361374</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.3715556015510219</v>
+        <v>0.0776953282638613</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6789</v>
+        <v>6654</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>762.7374045680307</v>
+        <v>807.5897996359054</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>543</v>
+        <v>217</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.18023872367346</v>
+        <v>81.47973967715242</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>17.3033947168185</v>
+        <v>49.90170831967203</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.29207010197899</v>
+        <v>2.906599723408326</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.5250959943303561</v>
+        <v>4.670128404541956</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6548</v>
+        <v>6799</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>740.3057127685315</v>
+        <v>785.4627432720902</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.43804979812613</v>
+        <v>57.84933944051281</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45.953030559496</v>
+        <v>28.15035620443928</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.081777033083125</v>
+        <v>0.9348095912750052</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0708441480748938</v>
+        <v>-0.7033341327412068</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6515</v>
+        <v>6585</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>731.7018282387438</v>
+        <v>784.9557825045504</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>9450</v>
+        <v>138</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.29554122068247</v>
+        <v>82.25863127237501</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.11150594718096</v>
+        <v>61.7062709942714</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4071994871890533</v>
+        <v>0.7437366899284942</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>129.6011827366065</v>
+        <v>2.500090576469724</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6684</v>
+        <v>6642</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>699.5971682405229</v>
+        <v>780.8608423077027</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>50.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>59.86218126243168</v>
+        <v>62.74579603884301</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.58436662278791</v>
+        <v>49.11298697147142</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8534729542142582</v>
+        <v>1.126022327329325</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>2</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.3909995506446446</v>
+        <v>-0.5446593916327673</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6579</v>
+        <v>6716</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>699.0362223020718</v>
+        <v>772.1827163849222</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>168</v>
+        <v>102.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.55546649983688</v>
+        <v>57.10837420268496</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34.39524414084448</v>
+        <v>31.26407260395085</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8753434627487922</v>
+        <v>0.8949242468624757</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.242653282998062</v>
+        <v>-0.3715556015510219</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6756</v>
+        <v>6625</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>678.1416604754152</v>
+        <v>767.1316005535589</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>103.5</v>
+        <v>79.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.26325622189354</v>
+        <v>73.73424442443589</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.31763444678247</v>
+        <v>28.40818044919114</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.083953984166174</v>
+        <v>0.8962910810064774</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.09348191124704019</v>
+        <v>0.6189978594853072</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6695</v>
+        <v>6789</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>620.0799611997192</v>
+        <v>762.7374045680307</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>58.4</v>
+        <v>543</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.12292877522373</v>
+        <v>57.18023872367346</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.32003038055074</v>
+        <v>17.3033947168185</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.019721572151448</v>
+        <v>1.29207010197899</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.109844231272294</v>
+        <v>-0.5250959943303561</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6683</v>
+        <v>6592</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>606.0058917802498</v>
+        <v>749.8479347788671</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1650</v>
+        <v>65.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.90341456428295</v>
+        <v>59.57831166142601</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.32088407161754</v>
+        <v>30.40405006500405</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6568674892856573</v>
+        <v>0.6527330248616018</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>12.59271849583236</v>
+        <v>0.1471769407247082</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6510</v>
+        <v>6548</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>604.31007612512</v>
+        <v>740.3057127685315</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3610</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.7300387962411</v>
+        <v>61.43804979812613</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.32110875948803</v>
+        <v>45.953030559496</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4831503060205751</v>
+        <v>1.081777033083125</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>36.94034840743035</v>
+        <v>-0.0708441480748938</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6538</v>
+        <v>6690</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>603.3839592569575</v>
+        <v>738.4497265344258</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>114.5</v>
+        <v>179</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.30017561572416</v>
+        <v>56.54219402110242</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31.51030935169861</v>
+        <v>20.17336800023329</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8466694706230615</v>
+        <v>0.3776136705165085</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-2.517077291107199</v>
+        <v>-0.1603454107286097</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6792</v>
+        <v>6515</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>600.7712409883621</v>
+        <v>731.7018282387438</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>70</v>
+        <v>9450</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.67536726111023</v>
+        <v>53.29554122068247</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.60102886163532</v>
+        <v>22.11150594718096</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.87360245281469</v>
+        <v>0.4071994871890533</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.4543987261012165</v>
+        <v>129.6011827366065</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6831</v>
+        <v>6684</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>585.0439710914773</v>
+        <v>699.5971682405229</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>773</v>
+        <v>50.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.93101780721293</v>
+        <v>59.86218126243168</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.87528833588537</v>
+        <v>23.58436662278791</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7121137770410801</v>
+        <v>0.8534729542142582</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>2</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-8.810974609613311</v>
+        <v>0.3909995506446446</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6573</v>
+        <v>6579</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>579.9933083791716</v>
+        <v>699.0362223020718</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>16.2</v>
+        <v>168</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.64954456025955</v>
+        <v>60.55546649983688</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.0425818237227</v>
+        <v>34.39524414084448</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8581207628046957</v>
+        <v>0.8753434627487922</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0996000074163519</v>
+        <v>-1.242653282998062</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6667</v>
+        <v>6811</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>569.812782752223</v>
+        <v>690.2550844174391</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>59.24161909272846</v>
+        <v>56.48196211626076</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.22264416449968</v>
+        <v>24.25791588660238</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.114029026806483</v>
+        <v>0.322590094879719</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.7889212397261094</v>
+        <v>-1.239738551469091</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6781</v>
+        <v>6757</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>542.7695069055412</v>
+        <v>689.6486036174433</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1180</v>
+        <v>58.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.45012835418107</v>
+        <v>59.04976281788139</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.0443300530513</v>
+        <v>27.65353632743929</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7565686046448018</v>
+        <v>1.264860361744333</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.343790575932574</v>
+        <v>0.304917903062322</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6558</v>
+        <v>6782</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>531.3039953144465</v>
+        <v>679.4596877983881</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>30.9</v>
+        <v>194.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.18447245255806</v>
+        <v>48.09779658962749</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.26949497356547</v>
+        <v>9.570025154908191</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3302023117931867</v>
+        <v>1.162907300207671</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.334556606445349</v>
+        <v>0.1732041175390648</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6658</v>
+        <v>6756</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>516.2894879319757</v>
+        <v>678.1416604754152</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>189</v>
+        <v>103.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.48364210655672</v>
+        <v>58.26325622189354</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>32.33825353474823</v>
+        <v>27.31763444678247</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.25501231647344</v>
+        <v>1.083953984166174</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-4.058730722051346</v>
+        <v>-0.09348191124704019</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6680</v>
+        <v>6666</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>511</v>
+        <v>621.0387890784043</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>51.5</v>
+        <v>42.95</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.91095176655806</v>
+        <v>59.74019650910902</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6.863919001273827</v>
+        <v>30.09871649823775</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.533934450571676</v>
+        <v>0.7428585176512101</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.9993186393016668</v>
+        <v>0.2367978614706607</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6727</v>
+        <v>6695</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>503.4645960592337</v>
+        <v>620.0799611997192</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>449</v>
+        <v>58.4</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.52615106428384</v>
+        <v>59.12292877522373</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.89367945259401</v>
+        <v>24.32003038055074</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6727984200975592</v>
+        <v>1.019721572151448</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>1</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-13.08914703597903</v>
+        <v>-0.109844231272294</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6570</v>
+        <v>6605</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>496.1486317061344</v>
+        <v>615.5838850128661</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>54.6</v>
+        <v>141.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.42481175718345</v>
+        <v>54.46870251499692</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.76705450469684</v>
+        <v>21.39862317239789</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3833070275867184</v>
+        <v>0.6278520735434507</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.109068786778863</v>
+        <v>-0.4618435740970446</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6581</v>
+        <v>6788</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>479.970592358576</v>
+        <v>606.7351938186156</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109</v>
+        <v>438</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.89955966305028</v>
+        <v>52.62888249344989</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.11252179967143</v>
+        <v>9.543018891078836</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3768419376858822</v>
+        <v>0.5844490702982315</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0665971308961273</v>
+        <v>1.191966052144083</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6669</v>
+        <v>6683</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>466.1181689692934</v>
+        <v>606.0058917802498</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>5130</v>
+        <v>1650</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.88120539285397</v>
+        <v>48.90341456428295</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.14533992693503</v>
+        <v>16.32088407161754</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8772528763705716</v>
+        <v>0.6568674892856573</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-67.9570811290519</v>
+        <v>12.59271849583236</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6679</v>
+        <v>6510</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>453.6898377236356</v>
+        <v>604.31007612512</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>285.5</v>
+        <v>3610</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.85136040216892</v>
+        <v>53.7300387962411</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.89648805720262</v>
+        <v>18.32110875948803</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.11668301656967</v>
+        <v>0.4831503060205751</v>
       </c>
       <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.101179549021317</v>
+        <v>36.94034840743035</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6664</v>
+        <v>6538</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>449.3570211672675</v>
+        <v>603.3839592569575</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>384.5</v>
+        <v>114.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>43.94022319526404</v>
+        <v>56.30017561572416</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.01642423037803</v>
+        <v>31.51030935169861</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4493816809447752</v>
+        <v>0.8466694706230615</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-3.31959791684152</v>
+        <v>-2.517077291107199</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6597</v>
+        <v>6792</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>440.8706393226338</v>
+        <v>600.7712409883621</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.3642279826005</v>
+        <v>56.67536726111023</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.95342029530177</v>
+        <v>34.60102886163532</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.3987806652451872</v>
+        <v>0.87360245281469</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.8235082161255737</v>
+        <v>-0.4543987261012165</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6640</v>
+        <v>6761</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>421.0881588648485</v>
+        <v>587.3656834060571</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1120</v>
+        <v>204</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40.2277505211943</v>
+        <v>51.09124751903306</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.20414624338033</v>
+        <v>20.3006593816762</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6745921331383645</v>
+        <v>0.5660019297695537</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-5.844428668762077</v>
+        <v>-2.232495006597721</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6776</v>
+        <v>6831</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>413.0446299831584</v>
+        <v>585.0439710914773</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>59.3</v>
+        <v>773</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.98653859611562</v>
+        <v>58.93101780721293</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9.190569822775885</v>
+        <v>24.87528833588537</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7364648797195718</v>
+        <v>0.7121137770410801</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1373214024441919</v>
+        <v>-8.810974609613311</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6588</v>
+        <v>6573</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>407.8954663890353</v>
+        <v>579.9933083791716</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.5</v>
+        <v>16.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.35619710147279</v>
+        <v>59.64954456025955</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.27212687535586</v>
+        <v>13.0425818237227</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4403768233267193</v>
+        <v>0.8581207628046957</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.6431512648268365</v>
+        <v>-0.0996000074163519</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6805</v>
+        <v>6505</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>398.7284014102837</v>
+        <v>574.4092512225554</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1755</v>
+        <v>53.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.56001974637073</v>
+        <v>52.69281747560816</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.95563451346673</v>
+        <v>12.47729341912265</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4235421821256706</v>
+        <v>1.423256493801552</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-22.32059347337242</v>
+        <v>0.0569474052823857</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6584</v>
+        <v>6667</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>392.2995944331854</v>
+        <v>569.812782752223</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>625</v>
+        <v>281</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.24033082115122</v>
+        <v>59.24161909272846</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.99895627351633</v>
+        <v>13.22264416449968</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4166067427830628</v>
+        <v>1.114029026806483</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-4.897651497646235</v>
+        <v>0.7889212397261094</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6720</v>
+        <v>6781</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>367.5597018916417</v>
+        <v>542.7695069055412</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>142</v>
+        <v>1180</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>31.40520770213884</v>
+        <v>52.45012835418107</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>32.37499213641874</v>
+        <v>13.0443300530513</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4962433826211615</v>
+        <v>0.7565686046448018</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.4338529336626631</v>
+        <v>1.343790575932574</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6560</v>
+        <v>6558</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>365.8166742834656</v>
+        <v>531.3039953144465</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>38</v>
+        <v>30.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.66411407423659</v>
+        <v>47.18447245255806</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.89738325434931</v>
+        <v>25.26949497356547</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4769321523662099</v>
+        <v>0.3302023117931867</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1219414082608044</v>
+        <v>-0.334556606445349</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6532</v>
+        <v>6658</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>357.8915831923025</v>
+        <v>516.2894879319757</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>91.2</v>
+        <v>189</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.09019394034403</v>
+        <v>53.48364210655672</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.77687482106036</v>
+        <v>32.33825353474823</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4693127005229541</v>
+        <v>1.25501231647344</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.9849691377950304</v>
+        <v>-4.058730722051346</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6512</v>
+        <v>6680</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>350.8206024752992</v>
+        <v>511</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>19.5</v>
+        <v>51.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.80891999353064</v>
+        <v>50.91095176655806</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.097562983992548</v>
+        <v>6.863919001273827</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5410566937326722</v>
+        <v>7.533934450571676</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.3545710958930965</v>
+        <v>0.9993186393016668</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6771</v>
+        <v>6727</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>344.8325442287269</v>
+        <v>503.4645960592337</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>42</v>
+        <v>449</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.22371642440847</v>
+        <v>47.52615106428384</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.02746498428115</v>
+        <v>20.89367945259401</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.296825479077181</v>
+        <v>0.6727984200975592</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>1</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0948303683630313</v>
+        <v>-13.08914703597903</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6743</v>
+        <v>6570</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>338.3828257707834</v>
+        <v>496.1486317061344</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>29</v>
+        <v>54.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.50494794959324</v>
+        <v>52.42481175718345</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.60396743861664</v>
+        <v>23.76705450469684</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4233598211674846</v>
+        <v>0.3833070275867184</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2274145851520772</v>
+        <v>-1.109068786778863</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6692</v>
+        <v>6823</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>337.5501471522792</v>
+        <v>491.8975746106038</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>27</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.54069699700314</v>
+        <v>50.71449582574334</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.41233210320248</v>
+        <v>23.92400623429385</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.334770468634914</v>
+        <v>1.307968081718171</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2841797902961656</v>
+        <v>0.07118777853642121</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6708</v>
+        <v>6754</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>331.1617641552466</v>
+        <v>483.0387850329988</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>39.8</v>
+        <v>45.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.69413375504143</v>
+        <v>54.45692286197189</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.1933117230612</v>
+        <v>22.95426029268657</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.513416997832753</v>
+        <v>0.4981974628195325</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>3</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0563190215787685</v>
+        <v>0.0865997717906264</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6643</v>
+        <v>6581</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>326.7879391794831</v>
+        <v>479.970592358576</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>494</v>
+        <v>109</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>40.73448371625519</v>
+        <v>51.89955966305028</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.40102873469428</v>
+        <v>12.11252179967143</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.598897058187882</v>
+        <v>0.3768419376858822</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-6.037609793522932</v>
+        <v>-0.0665971308961273</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6806</v>
+        <v>6669</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>321.1806280133556</v>
+        <v>466.1181689692934</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>3.24</v>
+        <v>5130</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>30.30810162010731</v>
+        <v>50.88120539285397</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32.28363367198867</v>
+        <v>18.14533992693503</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.437623507568395</v>
+        <v>0.8772528763705716</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.3767060656906009</v>
+        <v>-67.9570811290519</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6706</v>
+        <v>6763</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>319.8451855910437</v>
+        <v>464.2172627049663</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>172</v>
+        <v>47.4</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.69595574494014</v>
+        <v>52.94582153493487</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.33759879254464</v>
+        <v>23.4908495911508</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4565582620914242</v>
+        <v>0.3818612101319157</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-3.936865684636677</v>
+        <v>0.1566599524759921</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6546</v>
+        <v>6732</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>312.9547032703164</v>
+        <v>455.7168232961237</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>75</v>
+        <v>165.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.17604797029433</v>
+        <v>52.62164092033593</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.79833936336457</v>
+        <v>22.33337247195724</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.305171469891753</v>
+        <v>0.7532263202092644</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>2</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.7872609560339345</v>
+        <v>-1.023236210463264</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, market_above_ma60, adx_trending, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6641</v>
+        <v>6679</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>307.3953855107001</v>
+        <v>453.6898377236356</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>18.35</v>
+        <v>285.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.33883550074246</v>
+        <v>48.85136040216892</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.47475541857973</v>
+        <v>23.89648805720262</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.295478810426599</v>
+        <v>1.11668301656967</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.010076981174512</v>
+        <v>-2.101179549021317</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6561</v>
+        <v>6606</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>301.597941943676</v>
+        <v>453.1834028491537</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>338</v>
+        <v>25</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.95310179169165</v>
+        <v>40.63931539000673</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.92831024669716</v>
+        <v>19.34269588008988</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7831290660455803</v>
+        <v>0.5136885673212114</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.415889121095163</v>
+        <v>-0.1757053265563331</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6591</v>
+        <v>6664</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>297.5295297100117</v>
+        <v>449.3570211672675</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>55.5</v>
+        <v>384.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.89571698016637</v>
+        <v>43.94022319526404</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>21.27229468791863</v>
+        <v>25.01642423037803</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3419286435501053</v>
+        <v>0.4493816809447752</v>
       </c>
       <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1213228753602536</v>
+        <v>-3.31959791684152</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6568</v>
+        <v>6597</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>280.2611788583437</v>
+        <v>440.8706393226338</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>176.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>36.49207691973459</v>
+        <v>50.3642279826005</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>26.79358854175573</v>
+        <v>10.95342029530177</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3773273955494983</v>
+        <v>0.3987806652451872</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-2.716731307425485</v>
+        <v>-0.8235082161255737</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6530</v>
+        <v>6598</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>273.3349459004269</v>
+        <v>433.26031050972</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>24.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.42085234701366</v>
+        <v>48.21932065425869</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.37030248505064</v>
+        <v>22.98196286024654</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5481834479056017</v>
+        <v>0.730679224304985</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.258141815888457</v>
+        <v>-0.0973850437063709</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6624</v>
+        <v>6790</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>264.4797919522783</v>
+        <v>431.9082624105885</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>42.5</v>
+        <v>40.05</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.84351011611045</v>
+        <v>57.81957108057672</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.87641141601794</v>
+        <v>16.69084872186259</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1660141506019486</v>
+        <v>0.8015968810667898</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.8466583947305986</v>
+        <v>0.07182074780147869</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6689</v>
+        <v>6640</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>263.0097790658329</v>
+        <v>421.0881588648485</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>67</v>
+        <v>1120</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.94801996005704</v>
+        <v>40.2277505211943</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.15457280986532</v>
+        <v>26.20414624338033</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6604450680510734</v>
+        <v>0.6745921331383645</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2673178463243377</v>
+        <v>-5.844428668762077</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6533</v>
+        <v>6657</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>237.9493716166865</v>
+        <v>419.5474175138404</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>201.5</v>
+        <v>36.6</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>41.54824106436801</v>
+        <v>44.08976680435681</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.38626703298286</v>
+        <v>20.73155716212549</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3659666306626591</v>
+        <v>0.3089016272550021</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.991817398688603</v>
+        <v>0.0327490754015722</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6486</v>
+        <v>6753</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>219.7196600537474</v>
+        <v>419.3162582510543</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>81.8</v>
+        <v>121.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.91010668425125</v>
+        <v>43.88071845013081</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.18046689721345</v>
+        <v>16.17853104775411</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4919923609059986</v>
+        <v>0.5277531797640241</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>1</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1066056059074328</v>
+        <v>0.09138291655450009</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6552</v>
+        <v>6776</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>193.1053949052276</v>
+        <v>413.0446299831584</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>31.05</v>
+        <v>59.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.2543622094521</v>
+        <v>49.98653859611562</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.06653903305078</v>
+        <v>9.190569822775885</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5920959602831702</v>
+        <v>0.7364648797195718</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.3735132207745319</v>
+        <v>-0.1373214024441919</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6577</v>
+        <v>6589</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>184.5927133941264</v>
+        <v>408.1947952185165</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>75.7</v>
+        <v>46.45</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>32.22666725827857</v>
+        <v>57.45511551960622</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.44189594914305</v>
+        <v>18.0178743816983</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.359271339412637</v>
+        <v>0.8033679113291566</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.5273502491747291</v>
+        <v>0.4661562880509894</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6722</v>
+        <v>6588</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>175.2247126256183</v>
+        <v>407.8954663890353</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>37.4</v>
+        <v>107.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.84784003316734</v>
+        <v>42.35619710147279</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.11452675435338</v>
+        <v>16.27212687535586</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3261680613668061</v>
+        <v>0.4403768233267193</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1130206901409136</v>
+        <v>0.6431512648268365</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6835</v>
+        <v>6840</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>160.2019229840527</v>
+        <v>405.4206114395907</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>36.55</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>42.5552187182104</v>
+        <v>50.69828413989109</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.96652691060163</v>
+        <v>18.51784994013943</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.1401610274202643</v>
+        <v>0.379633914857369</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,64 +4651,2449 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1441846346349169</v>
+        <v>-0.1156446447329875</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
+        <v>6805</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>398.7284014102837</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>1755</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>44.56001974637073</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>14.95563451346673</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.4235421821256706</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-22.32059347337242</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6584</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>392.2995944331854</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>47.24033082115122</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>11.99895627351633</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.4166067427830628</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-4.897651497646235</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6720</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>久昌</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>367.5597018916417</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>31.40520770213884</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>32.37499213641874</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.4962433826211615</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-0.4338529336626631</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>欣普羅</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>365.8166742834656</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>48.66411407423659</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>13.89738325434931</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.4769321523662099</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-0.1219414082608044</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>358.1206578860162</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>57.0939201806214</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>16.43856065474495</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>1.261678801881495</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.2100880551975733</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6532</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>瑞耘</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>357.8915831923025</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46.09019394034403</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>22.77687482106036</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.4693127005229541</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0.9849691377950304</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6512</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>啟發電</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>350.8206024752992</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>51.80891999353064</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>9.097562983992548</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.5410566937326722</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-0.3545710958930965</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>平和環保-創</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>344.8325442287269</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46.22371642440847</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>14.02746498428115</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>2.296825479077181</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0948303683630313</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6743</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>安普新</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>338.3828257707834</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>49.50494794959324</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>19.60396743861664</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.4233598211674846</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.2274145851520772</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6692</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>進能服</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>337.5501471522792</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>48.54069699700314</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>22.41233210320248</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.334770468634914</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.2841797902961656</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6708</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>天擎</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>331.1617641552466</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>47.69413375504143</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>15.1933117230612</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.513416997832753</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-0.0563190215787685</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6735</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>美達科技</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>329.1684870095842</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>43.64730547611745</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>17.09880450318325</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.5440638629536038</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-1.217928507314312</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6643</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>326.7879391794831</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>494</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>40.73448371625519</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>26.40102873469428</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.598897058187882</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-6.037609793522932</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6582</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>申豐</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>322.428039266248</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>51.70125704408211</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>24.05578276321781</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.8574275770932969</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.0357247385683947</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6806</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>森崴能源</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>321.1806280133556</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30.30810162010731</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>32.28363367198867</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.437623507568395</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.3767060656906009</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6706</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>惠特</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>319.8451855910437</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>48.69595574494014</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>18.33759879254464</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.4565582620914242</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-3.936865684636677</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6546</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>正基</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>312.9547032703164</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>50.17604797029433</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>18.79833936336457</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.305171469891753</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.7872609560339345</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6641</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>基士德-KY</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>307.3953855107001</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>48.33883550074246</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>18.47475541857973</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.295478810426599</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.010076981174512</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6561</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>是方</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>301.597941943676</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>39.95310179169165</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>15.92831024669716</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.7831290660455803</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-2.415889121095163</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6591</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>動力-KY</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>297.5295297100117</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>47.89571698016637</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>21.27229468791863</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.3419286435501053</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.1213228753602536</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6794</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>向榮生技-創</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>292.1953224228291</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>43.80472455370605</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>12.3421806971738</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.9018978853386032</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.2441823158338045</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6655</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>科定</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>286.3466308157642</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>41.56732406472484</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>11.3868092559331</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.4530174904144125</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.1615298829078009</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6803</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>280.7227010509254</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>46.15617831811868</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>24.93383604328993</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.3365510385601423</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.0200492284719173</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6568</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>宏觀</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>280.2611788583437</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>36.49207691973459</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>26.79358854175573</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.3773273955494983</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-2.716731307425485</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6739</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>279.4957356391664</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>40.01878436192246</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>13.15636385910696</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.4617560143540447</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-7.96328009818636</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6741</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>91APP*-KY</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>274.5386283811026</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>47.23210500951463</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>11.56697746259884</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.3088788572932415</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.2008244012456962</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6530</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>創威</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>273.3349459004269</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>43.42085234701366</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>15.37030248505064</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.5481834479056017</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-1.258141815888457</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6829</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>千附精密</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>272.7777222211289</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>48.70296765300441</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>15.22480620504827</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.8228802885376895</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-1.221840131600894</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>萬年清</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>264.4797919522783</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>50.84351011611045</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>12.87641141601794</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.1660141506019486</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.8466583947305986</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6671</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>三能-KY</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>264.1282557155092</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>31.28109326990326</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>16.53314465524487</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.13869551264866</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.0615953555498577</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>263.0097790658329</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>43.94801996005704</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>13.15457280986532</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.6604450680510734</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-0.2673178463243377</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6550</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>北極星藥業-KY</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>257.9491049682562</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>39.19949754468562</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>34.80211484547163</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.7151758191876006</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.1882558760555894</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6533</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>237.9493716166865</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>41.54824106436801</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>17.38626703298286</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.3659666306626591</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-1.991817398688603</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6768</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>志強-KY</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>236.0692268231926</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>42.65018467420555</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>19.68857508131785</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.439277772592053</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.9863750511687024</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6534</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>正瀚-創</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>231.5122781301536</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>51.45026572332196</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>15.52807096553202</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.2043133024836616</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.2146645791908981</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6486</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>互動</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>219.7196600537474</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>44.91010668425125</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>17.18046689721345</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4919923609059986</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.1066056059074328</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6796</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>晉弘</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>210.6015728729433</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>40.60646693343379</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>30.94907525177072</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5849974715911801</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.297146230995819</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>易華電</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>193.1053949052276</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>50.2543622094521</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>16.06653903305078</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.5920959602831702</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.3735132207745319</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>南六</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>189.5613741545583</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>38.29897723461637</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>19.12552846874458</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.6915485751808468</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.0817778241864994</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>6577</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>勁豐</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>184.5927133941264</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>32.22666725827857</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>14.44189594914305</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>1.359271339412637</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.5273502491747291</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>6807</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>峰源-KY</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>176.0560341964963</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>44.56133179512</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>25.25671015176294</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.5815075318441455</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0.1995401502679753</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6722</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>輝創</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>175.2247126256183</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>40.84784003316734</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>15.11452675435338</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.3261680613668061</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.1130206901409136</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>圓裕</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>160.2019229840527</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>42.5552187182104</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>13.96652691060163</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.1401610274202643</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.1441846346349169</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
         <v>6674</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>鋐寶科技</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
         <v>155.3178938175574</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E123" s="2" t="n">
         <v>17.45</v>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
         <v>45.9465259515588</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I123" s="2" t="n">
         <v>17.1776694624163</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J123" s="2" t="n">
         <v>0.6990016188308878</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K123" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
         <v>-0.0056636724478135</v>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O123" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>146.9956837223489</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>36.34457229431654</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>9.987312224858233</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.8223454801759448</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0562771371694759</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>泰福-KY</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>145.3276399708073</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>52.23109404744078</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>15.05479498000048</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.7868236035429527</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.0409418610394836</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-18.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6670</v>
+        <v>6693</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>910.7652164853164</v>
+        <v>887.380043859049</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>287.5</v>
+        <v>215</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.59500954264795</v>
+        <v>73.78800992308639</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.17260645618079</v>
+        <v>43.55139436623084</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.67652164853163</v>
+        <v>0.5421636572238565</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.674085568335069</v>
+        <v>4.784345920189317</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6693</v>
+        <v>6526</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>887.380043859049</v>
+        <v>885.8101812312409</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>215</v>
+        <v>696</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>73.78800992308639</v>
+        <v>57.27441593254295</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>43.55139436623084</v>
+        <v>15.92800824988902</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5421636572238565</v>
+        <v>0.8440015865291703</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4.784345920189317</v>
+        <v>-1.892330284699976</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6526</v>
+        <v>6719</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>885.8101812312409</v>
+        <v>877.5354761424178</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>696</v>
+        <v>260.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.27441593254295</v>
+        <v>65.27355028331195</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.92800824988902</v>
+        <v>41.70842200625049</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8440015865291703</v>
+        <v>1.510745392050772</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.892330284699976</v>
+        <v>-0.1626630564506292</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6719</v>
+        <v>6531</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>877.5354761424178</v>
+        <v>868.6849445445503</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>260.5</v>
+        <v>1025</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.27355028331195</v>
+        <v>55.51986259629508</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.70842200625049</v>
+        <v>22.89687948441851</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.510745392050772</v>
+        <v>0.8567805932106699</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1626630564506292</v>
+        <v>-15.09787458754278</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6531</v>
+        <v>6770</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>868.6849445445503</v>
+        <v>823.3468390850512</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1025</v>
+        <v>74.2</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.51986259629508</v>
+        <v>55.01067941807321</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.89687948441851</v>
+        <v>22.93234185296706</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8567805932106699</v>
+        <v>0.9355652342190248</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-15.09787458754278</v>
+        <v>-0.927604961651192</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6821</v>
+        <v>6698</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>866.1456140363823</v>
+        <v>822.7334586354094</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>41.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.97912554273852</v>
+        <v>62.39525515005698</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.00597229021887</v>
+        <v>32.46599330553001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6552452231107171</v>
+        <v>0.6776164700115573</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.7606882606968148</v>
+        <v>-0.2891875560227654</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6491</v>
+        <v>6517</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>842.472932803794</v>
+        <v>814.6300515209522</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>327.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.46959566109601</v>
+        <v>69.09896481291364</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.49264103124435</v>
+        <v>35.63943158836702</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.334735840394839</v>
+        <v>1.56300515209522</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.7682738945023</v>
+        <v>1.552721625557503</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6645</v>
+        <v>6498</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>836.4401941659953</v>
+        <v>811.505914198876</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.35</v>
+        <v>107</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.48288221737064</v>
+        <v>57.36554008121749</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39.75349252258958</v>
+        <v>31.50554048612483</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7440194165995356</v>
+        <v>1.99235970050026</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3401550610842302</v>
+        <v>0.3474482885282075</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6770</v>
+        <v>6691</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>823.3468390850512</v>
+        <v>811.283643862397</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>74.2</v>
+        <v>720</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.01067941807321</v>
+        <v>61.96953185049647</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.93234185296706</v>
+        <v>19.25466148366536</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9355652342190248</v>
+        <v>0.7988965846535838</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.927604961651192</v>
+        <v>8.869528397788958</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6698</v>
+        <v>6556</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>822.7334586354094</v>
+        <v>810.0088365675093</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>41.95</v>
+        <v>73.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62.39525515005698</v>
+        <v>63.27412618652882</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.46599330553001</v>
+        <v>43.99281806072749</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6776164700115573</v>
+        <v>0.9750608080361374</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.2891875560227654</v>
+        <v>0.0776953282638613</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6517</v>
+        <v>6654</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>814.6300515209522</v>
+        <v>807.5897996359054</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>217</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.09896481291364</v>
+        <v>81.47973967715242</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>35.63943158836702</v>
+        <v>49.90170831967203</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.56300515209522</v>
+        <v>2.906599723408326</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.552721625557503</v>
+        <v>4.670128404541956</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6498</v>
+        <v>6799</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>811.505914198876</v>
+        <v>785.4627432720902</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>107</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.36554008121749</v>
+        <v>57.84933944051281</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.50554048612483</v>
+        <v>28.15035620443928</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.99235970050026</v>
+        <v>0.9348095912750052</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3474482885282075</v>
+        <v>-0.7033341327412068</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6691</v>
+        <v>6642</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>811.283643862397</v>
+        <v>780.8608423077027</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>720</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.96953185049647</v>
+        <v>62.74579603884301</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.25466148366536</v>
+        <v>49.11298697147142</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7988965846535838</v>
+        <v>1.126022327329325</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>8.869528397788958</v>
+        <v>-0.5446593916327673</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6556</v>
+        <v>6716</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>810.0088365675093</v>
+        <v>772.1827163849222</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>73.5</v>
+        <v>102.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>63.27412618652882</v>
+        <v>57.10837420268496</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>43.99281806072749</v>
+        <v>31.26407260395085</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9750608080361374</v>
+        <v>0.8949242468624757</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0776953282638613</v>
+        <v>-0.3715556015510219</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6654</v>
+        <v>6789</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>807.5897996359054</v>
+        <v>762.7374045680307</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>217</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>81.47973967715242</v>
+        <v>57.18023872367346</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>49.90170831967203</v>
+        <v>17.3033947168185</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.906599723408326</v>
+        <v>1.29207010197899</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4.670128404541956</v>
+        <v>-0.5250959943303561</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6799</v>
+        <v>6548</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>785.4627432720902</v>
+        <v>740.3057127685315</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.84933944051281</v>
+        <v>61.43804979812613</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.15035620443928</v>
+        <v>45.953030559496</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.9348095912750052</v>
+        <v>1.081777033083125</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.7033341327412068</v>
+        <v>-0.0708441480748938</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6585</v>
+        <v>6515</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>784.9557825045504</v>
+        <v>731.7018282387438</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>138</v>
+        <v>9450</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>82.25863127237501</v>
+        <v>53.29554122068247</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>61.7062709942714</v>
+        <v>22.11150594718096</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7437366899284942</v>
+        <v>0.4071994871890533</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.500090576469724</v>
+        <v>129.6011827366065</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6642</v>
+        <v>6684</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>780.8608423077027</v>
+        <v>699.5971682405229</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.74579603884301</v>
+        <v>59.86218126243168</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49.11298697147142</v>
+        <v>23.58436662278791</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.126022327329325</v>
+        <v>0.8534729542142582</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>2</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.5446593916327673</v>
+        <v>0.3909995506446446</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6716</v>
+        <v>6579</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>772.1827163849222</v>
+        <v>699.0362223020718</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>102.5</v>
+        <v>168</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.10837420268496</v>
+        <v>60.55546649983688</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.26407260395085</v>
+        <v>34.39524414084448</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8949242468624757</v>
+        <v>0.8753434627487922</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.3715556015510219</v>
+        <v>-1.242653282998062</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6625</v>
+        <v>6756</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>767.1316005535589</v>
+        <v>678.1416604754152</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79.2</v>
+        <v>103.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>73.73424442443589</v>
+        <v>58.26325622189354</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.40818044919114</v>
+        <v>27.31763444678247</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8962910810064774</v>
+        <v>1.083953984166174</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.6189978594853072</v>
+        <v>-0.09348191124704019</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6789</v>
+        <v>6695</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>762.7374045680307</v>
+        <v>620.0799611997192</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>543</v>
+        <v>58.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.18023872367346</v>
+        <v>59.12292877522373</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.3033947168185</v>
+        <v>24.32003038055074</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.29207010197899</v>
+        <v>1.019721572151448</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.5250959943303561</v>
+        <v>-0.109844231272294</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6592</v>
+        <v>6683</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>749.8479347788671</v>
+        <v>606.0058917802498</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>65.3</v>
+        <v>1650</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.57831166142601</v>
+        <v>48.90341456428295</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.40405006500405</v>
+        <v>16.32088407161754</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6527330248616018</v>
+        <v>0.6568674892856573</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1471769407247082</v>
+        <v>12.59271849583236</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6548</v>
+        <v>6510</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>740.3057127685315</v>
+        <v>604.31007612512</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>3610</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>61.43804979812613</v>
+        <v>53.7300387962411</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45.953030559496</v>
+        <v>18.32110875948803</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.081777033083125</v>
+        <v>0.4831503060205751</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0708441480748938</v>
+        <v>36.94034840743035</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6690</v>
+        <v>6538</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>738.4497265344258</v>
+        <v>603.3839592569575</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>179</v>
+        <v>114.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.54219402110242</v>
+        <v>56.30017561572416</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.17336800023329</v>
+        <v>31.51030935169861</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.3776136705165085</v>
+        <v>0.8466694706230615</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1603454107286097</v>
+        <v>-2.517077291107199</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6515</v>
+        <v>6792</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>731.7018282387438</v>
+        <v>600.7712409883621</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9450</v>
+        <v>70</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.29554122068247</v>
+        <v>56.67536726111023</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.11150594718096</v>
+        <v>34.60102886163532</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4071994871890533</v>
+        <v>0.87360245281469</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>129.6011827366065</v>
+        <v>-0.4543987261012165</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6684</v>
+        <v>6831</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>699.5971682405229</v>
+        <v>585.0439710914773</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>50.5</v>
+        <v>773</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.86218126243168</v>
+        <v>58.93101780721293</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.58436662278791</v>
+        <v>24.87528833588537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8534729542142582</v>
+        <v>0.7121137770410801</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>2</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3909995506446446</v>
+        <v>-8.810974609613311</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6579</v>
+        <v>6573</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>699.0362223020718</v>
+        <v>579.9933083791716</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>168</v>
+        <v>16.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>60.55546649983688</v>
+        <v>59.64954456025955</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>34.39524414084448</v>
+        <v>13.0425818237227</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8753434627487922</v>
+        <v>0.8581207628046957</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.242653282998062</v>
+        <v>-0.0996000074163519</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6811</v>
+        <v>6667</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>690.2550844174391</v>
+        <v>569.812782752223</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.48196211626076</v>
+        <v>59.24161909272846</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.25791588660238</v>
+        <v>13.22264416449968</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.322590094879719</v>
+        <v>1.114029026806483</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.239738551469091</v>
+        <v>0.7889212397261094</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6757</v>
+        <v>6781</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>689.6486036174433</v>
+        <v>542.7695069055412</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>58.2</v>
+        <v>1180</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>59.04976281788139</v>
+        <v>52.45012835418107</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.65353632743929</v>
+        <v>13.0443300530513</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.264860361744333</v>
+        <v>0.7565686046448018</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.304917903062322</v>
+        <v>1.343790575932574</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6782</v>
+        <v>6558</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>679.4596877983881</v>
+        <v>531.3039953144465</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>194.5</v>
+        <v>30.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.09779658962749</v>
+        <v>47.18447245255806</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.570025154908191</v>
+        <v>25.26949497356547</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.162907300207671</v>
+        <v>0.3302023117931867</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1732041175390648</v>
+        <v>-0.334556606445349</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6756</v>
+        <v>6658</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>678.1416604754152</v>
+        <v>516.2894879319757</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>103.5</v>
+        <v>189</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.26325622189354</v>
+        <v>53.48364210655672</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.31763444678247</v>
+        <v>32.33825353474823</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.083953984166174</v>
+        <v>1.25501231647344</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.09348191124704019</v>
+        <v>-4.058730722051346</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6666</v>
+        <v>6680</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>621.0387890784043</v>
+        <v>511</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>42.95</v>
+        <v>51.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>59.74019650910902</v>
+        <v>50.91095176655806</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30.09871649823775</v>
+        <v>6.863919001273827</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7428585176512101</v>
+        <v>7.533934450571676</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2367978614706607</v>
+        <v>0.9993186393016668</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6695</v>
+        <v>6727</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>620.0799611997192</v>
+        <v>503.4645960592337</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>58.4</v>
+        <v>449</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.12292877522373</v>
+        <v>47.52615106428384</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.32003038055074</v>
+        <v>20.89367945259401</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.019721572151448</v>
+        <v>0.6727984200975592</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>1</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.109844231272294</v>
+        <v>-13.08914703597903</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6605</v>
+        <v>6570</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>615.5838850128661</v>
+        <v>496.1486317061344</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>141.5</v>
+        <v>54.6</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.46870251499692</v>
+        <v>52.42481175718345</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.39862317239789</v>
+        <v>23.76705450469684</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6278520735434507</v>
+        <v>0.3833070275867184</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.4618435740970446</v>
+        <v>-1.109068786778863</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6788</v>
+        <v>6581</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>606.7351938186156</v>
+        <v>479.970592358576</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>438</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.62888249344989</v>
+        <v>51.89955966305028</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.543018891078836</v>
+        <v>12.11252179967143</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5844490702982315</v>
+        <v>0.3768419376858822</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.191966052144083</v>
+        <v>-0.0665971308961273</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6683</v>
+        <v>6669</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>606.0058917802498</v>
+        <v>466.1181689692934</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1650</v>
+        <v>5130</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.90341456428295</v>
+        <v>50.88120539285397</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.32088407161754</v>
+        <v>18.14533992693503</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6568674892856573</v>
+        <v>0.8772528763705716</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>12.59271849583236</v>
+        <v>-67.9570811290519</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6510</v>
+        <v>6679</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>604.31007612512</v>
+        <v>453.6898377236356</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>3610</v>
+        <v>285.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.7300387962411</v>
+        <v>48.85136040216892</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.32110875948803</v>
+        <v>23.89648805720262</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4831503060205751</v>
+        <v>1.11668301656967</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>36.94034840743035</v>
+        <v>-2.101179549021317</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6538</v>
+        <v>6664</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>603.3839592569575</v>
+        <v>449.3570211672675</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>114.5</v>
+        <v>384.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>56.30017561572416</v>
+        <v>43.94022319526404</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>31.51030935169861</v>
+        <v>25.01642423037803</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8466694706230615</v>
+        <v>0.4493816809447752</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.517077291107199</v>
+        <v>-3.31959791684152</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6792</v>
+        <v>6597</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>600.7712409883621</v>
+        <v>440.8706393226338</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>56.67536726111023</v>
+        <v>50.3642279826005</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>34.60102886163532</v>
+        <v>10.95342029530177</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.87360245281469</v>
+        <v>0.3987806652451872</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>1</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4543987261012165</v>
+        <v>-0.8235082161255737</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6761</v>
+        <v>6640</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>587.3656834060571</v>
+        <v>421.0881588648485</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>204</v>
+        <v>1120</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.09124751903306</v>
+        <v>40.2277505211943</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.3006593816762</v>
+        <v>26.20414624338033</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5660019297695537</v>
+        <v>0.6745921331383645</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-2.232495006597721</v>
+        <v>-5.844428668762077</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6831</v>
+        <v>6776</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>585.0439710914773</v>
+        <v>413.0446299831584</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>773</v>
+        <v>59.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>58.93101780721293</v>
+        <v>49.98653859611562</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.87528833588537</v>
+        <v>9.190569822775885</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7121137770410801</v>
+        <v>0.7364648797195718</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-8.810974609613311</v>
+        <v>-0.1373214024441919</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6573</v>
+        <v>6588</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>579.9933083791716</v>
+        <v>407.8954663890353</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>16.2</v>
+        <v>107.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>59.64954456025955</v>
+        <v>42.35619710147279</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.0425818237227</v>
+        <v>16.27212687535586</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8581207628046957</v>
+        <v>0.4403768233267193</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0996000074163519</v>
+        <v>0.6431512648268365</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6505</v>
+        <v>6805</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>574.4092512225554</v>
+        <v>398.7284014102837</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>53.5</v>
+        <v>1755</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.69281747560816</v>
+        <v>44.56001974637073</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.47729341912265</v>
+        <v>14.95563451346673</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.423256493801552</v>
+        <v>0.4235421821256706</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0569474052823857</v>
+        <v>-22.32059347337242</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6667</v>
+        <v>6584</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>569.812782752223</v>
+        <v>392.2995944331854</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>281</v>
+        <v>625</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>59.24161909272846</v>
+        <v>47.24033082115122</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.22264416449968</v>
+        <v>11.99895627351633</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.114029026806483</v>
+        <v>0.4166067427830628</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.7889212397261094</v>
+        <v>-4.897651497646235</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6781</v>
+        <v>6720</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>542.7695069055412</v>
+        <v>367.5597018916417</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1180</v>
+        <v>142</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.45012835418107</v>
+        <v>31.40520770213884</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.0443300530513</v>
+        <v>32.37499213641874</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7565686046448018</v>
+        <v>0.4962433826211615</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.343790575932574</v>
+        <v>-0.4338529336626631</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6558</v>
+        <v>6560</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>531.3039953144465</v>
+        <v>365.8166742834656</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>30.9</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.18447245255806</v>
+        <v>48.66411407423659</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25.26949497356547</v>
+        <v>13.89738325434931</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3302023117931867</v>
+        <v>0.4769321523662099</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.334556606445349</v>
+        <v>-0.1219414082608044</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6658</v>
+        <v>6532</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>516.2894879319757</v>
+        <v>357.8915831923025</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>189</v>
+        <v>91.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.48364210655672</v>
+        <v>46.09019394034403</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>32.33825353474823</v>
+        <v>22.77687482106036</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.25501231647344</v>
+        <v>0.4693127005229541</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-4.058730722051346</v>
+        <v>-0.9849691377950304</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6680</v>
+        <v>6512</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>511</v>
+        <v>350.8206024752992</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>51.5</v>
+        <v>19.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.91095176655806</v>
+        <v>51.80891999353064</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6.863919001273827</v>
+        <v>9.097562983992548</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.533934450571676</v>
+        <v>0.5410566937326722</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9993186393016668</v>
+        <v>-0.3545710958930965</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6727</v>
+        <v>6771</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>503.4645960592337</v>
+        <v>344.8325442287269</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>449</v>
+        <v>42</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.52615106428384</v>
+        <v>46.22371642440847</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.89367945259401</v>
+        <v>14.02746498428115</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6727984200975592</v>
+        <v>2.296825479077181</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>1</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-13.08914703597903</v>
+        <v>0.0948303683630313</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6570</v>
+        <v>6743</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>496.1486317061344</v>
+        <v>338.3828257707834</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>54.6</v>
+        <v>29</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.42481175718345</v>
+        <v>49.50494794959324</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.76705450469684</v>
+        <v>19.60396743861664</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3833070275867184</v>
+        <v>0.4233598211674846</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.109068786778863</v>
+        <v>-0.2274145851520772</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6823</v>
+        <v>6692</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>491.8975746106038</v>
+        <v>337.5501471522792</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>27</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.71449582574334</v>
+        <v>48.54069699700314</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.92400623429385</v>
+        <v>22.41233210320248</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.307968081718171</v>
+        <v>1.334770468634914</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.07118777853642121</v>
+        <v>0.2841797902961656</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6754</v>
+        <v>6708</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>483.0387850329988</v>
+        <v>331.1617641552466</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>45.5</v>
+        <v>39.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.45692286197189</v>
+        <v>47.69413375504143</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.95426029268657</v>
+        <v>15.1933117230612</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4981974628195325</v>
+        <v>0.513416997832753</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>3</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0865997717906264</v>
+        <v>-0.0563190215787685</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6581</v>
+        <v>6643</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>479.970592358576</v>
+        <v>326.7879391794831</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>109</v>
+        <v>494</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.89955966305028</v>
+        <v>40.73448371625519</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.11252179967143</v>
+        <v>26.40102873469428</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3768419376858822</v>
+        <v>0.598897058187882</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0665971308961273</v>
+        <v>-6.037609793522932</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6669</v>
+        <v>6806</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>466.1181689692934</v>
+        <v>321.1806280133556</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>5130</v>
+        <v>3.24</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.88120539285397</v>
+        <v>30.30810162010731</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.14533992693503</v>
+        <v>32.28363367198867</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8772528763705716</v>
+        <v>1.437623507568395</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-67.9570811290519</v>
+        <v>0.3767060656906009</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6763</v>
+        <v>6706</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>464.2172627049663</v>
+        <v>319.8451855910437</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>47.4</v>
+        <v>172</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.94582153493487</v>
+        <v>48.69595574494014</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.4908495911508</v>
+        <v>18.33759879254464</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3818612101319157</v>
+        <v>0.4565582620914242</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1566599524759921</v>
+        <v>-3.936865684636677</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6732</v>
+        <v>6546</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>455.7168232961237</v>
+        <v>312.9547032703164</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>165.5</v>
+        <v>75</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>52.62164092033593</v>
+        <v>50.17604797029433</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.33337247195724</v>
+        <v>18.79833936336457</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7532263202092644</v>
+        <v>0.305171469891753</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>2</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.023236210463264</v>
+        <v>-0.7872609560339345</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, adx_trending, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6679</v>
+        <v>6641</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>453.6898377236356</v>
+        <v>307.3953855107001</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>285.5</v>
+        <v>18.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.85136040216892</v>
+        <v>48.33883550074246</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.89648805720262</v>
+        <v>18.47475541857973</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.11668301656967</v>
+        <v>1.295478810426599</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.101179549021317</v>
+        <v>0.010076981174512</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6606</v>
+        <v>6561</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>453.1834028491537</v>
+        <v>301.597941943676</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>25</v>
+        <v>338</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.63931539000673</v>
+        <v>39.95310179169165</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.34269588008988</v>
+        <v>15.92831024669716</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5136885673212114</v>
+        <v>0.7831290660455803</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1757053265563331</v>
+        <v>-2.415889121095163</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6664</v>
+        <v>6591</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>449.3570211672675</v>
+        <v>297.5295297100117</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>384.5</v>
+        <v>55.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.94022319526404</v>
+        <v>47.89571698016637</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>25.01642423037803</v>
+        <v>21.27229468791863</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4493816809447752</v>
+        <v>0.3419286435501053</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-3.31959791684152</v>
+        <v>-0.1213228753602536</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6597</v>
+        <v>6568</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>440.8706393226338</v>
+        <v>280.2611788583437</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>176.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.3642279826005</v>
+        <v>36.49207691973459</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10.95342029530177</v>
+        <v>26.79358854175573</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3987806652451872</v>
+        <v>0.3773273955494983</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.8235082161255737</v>
+        <v>-2.716731307425485</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6598</v>
+        <v>6530</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>433.26031050972</v>
+        <v>273.3349459004269</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>24.15</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.21932065425869</v>
+        <v>43.42085234701366</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.98196286024654</v>
+        <v>15.37030248505064</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.730679224304985</v>
+        <v>0.5481834479056017</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0973850437063709</v>
+        <v>-1.258141815888457</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6790</v>
+        <v>6624</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>431.9082624105885</v>
+        <v>264.4797919522783</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>40.05</v>
+        <v>42.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>57.81957108057672</v>
+        <v>50.84351011611045</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.69084872186259</v>
+        <v>12.87641141601794</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8015968810667898</v>
+        <v>0.1660141506019486</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.07182074780147869</v>
+        <v>-0.8466583947305986</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6640</v>
+        <v>6689</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>421.0881588648485</v>
+        <v>263.0097790658329</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1120</v>
+        <v>67</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.2277505211943</v>
+        <v>43.94801996005704</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26.20414624338033</v>
+        <v>13.15457280986532</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6745921331383645</v>
+        <v>0.6604450680510734</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-5.844428668762077</v>
+        <v>-0.2673178463243377</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6657</v>
+        <v>6533</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>419.5474175138404</v>
+        <v>237.9493716166865</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>36.6</v>
+        <v>201.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.08976680435681</v>
+        <v>41.54824106436801</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.73155716212549</v>
+        <v>17.38626703298286</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3089016272550021</v>
+        <v>0.3659666306626591</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0327490754015722</v>
+        <v>-1.991817398688603</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6753</v>
+        <v>6486</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>419.3162582510543</v>
+        <v>219.7196600537474</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>121.5</v>
+        <v>81.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.88071845013081</v>
+        <v>44.91010668425125</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.17853104775411</v>
+        <v>17.18046689721345</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5277531797640241</v>
+        <v>0.4919923609059986</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>1</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.09138291655450009</v>
+        <v>0.1066056059074328</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6776</v>
+        <v>6552</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>413.0446299831584</v>
+        <v>193.1053949052276</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>59.3</v>
+        <v>31.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.98653859611562</v>
+        <v>50.2543622094521</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.190569822775885</v>
+        <v>16.06653903305078</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7364648797195718</v>
+        <v>0.5920959602831702</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1373214024441919</v>
+        <v>-0.3735132207745319</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6589</v>
+        <v>6577</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>408.1947952185165</v>
+        <v>184.5927133941264</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>46.45</v>
+        <v>75.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>57.45511551960622</v>
+        <v>32.22666725827857</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.0178743816983</v>
+        <v>14.44189594914305</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8033679113291566</v>
+        <v>1.359271339412637</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.4661562880509894</v>
+        <v>-0.5273502491747291</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6588</v>
+        <v>6722</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>407.8954663890353</v>
+        <v>175.2247126256183</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>107.5</v>
+        <v>37.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.35619710147279</v>
+        <v>40.84784003316734</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.27212687535586</v>
+        <v>15.11452675435338</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4403768233267193</v>
+        <v>0.3261680613668061</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.6431512648268365</v>
+        <v>-0.1130206901409136</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6840</v>
+        <v>6835</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>405.4206114395907</v>
+        <v>160.2019229840527</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>36.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.69828413989109</v>
+        <v>42.5552187182104</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.51784994013943</v>
+        <v>13.96652691060163</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.379633914857369</v>
+        <v>0.1401610274202643</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1156446447329875</v>
+        <v>-0.1441846346349169</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6805</v>
+        <v>6674</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>398.7284014102837</v>
+        <v>155.3178938175574</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1755</v>
+        <v>17.45</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.56001974637073</v>
+        <v>45.9465259515588</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.95563451346673</v>
+        <v>17.1776694624163</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4235421821256706</v>
+        <v>0.6990016188308878</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,2396 +4704,11 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-22.32059347337242</v>
+        <v>-0.0056636724478135</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>6584</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>南俊國際</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>392.2995944331854</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>625</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>47.24033082115122</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>11.99895627351633</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>0.4166067427830628</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>-4.897651497646235</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>6720</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>久昌</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>367.5597018916417</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>31.40520770213884</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>32.37499213641874</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0.4962433826211615</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-0.4338529336626631</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>6560</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>欣普羅</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>365.8166742834656</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>48.66411407423659</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>13.89738325434931</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.4769321523662099</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>-0.1219414082608044</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>6614</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>358.1206578860162</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>57.0939201806214</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>16.43856065474495</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>1.261678801881495</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>0.2100880551975733</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>6532</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>瑞耘</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>357.8915831923025</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>46.09019394034403</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>22.77687482106036</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>0.4693127005229541</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-0.9849691377950304</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>6512</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>啟發電</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>350.8206024752992</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>51.80891999353064</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>9.097562983992548</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.5410566937326722</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>-0.3545710958930965</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>6771</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>平和環保-創</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>344.8325442287269</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>46.22371642440847</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>14.02746498428115</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>2.296825479077181</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>0.0948303683630313</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>6743</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>安普新</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>338.3828257707834</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>49.50494794959324</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>19.60396743861664</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.4233598211674846</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>-0.2274145851520772</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>6692</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>進能服</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>337.5501471522792</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>48.54069699700314</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>22.41233210320248</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>1.334770468634914</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>0.2841797902961656</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>6708</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>天擎</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>331.1617641552466</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>47.69413375504143</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>15.1933117230612</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0.513416997832753</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>-0.0563190215787685</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>6735</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>美達科技</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>329.1684870095842</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>43.64730547611745</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>17.09880450318325</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.5440638629536038</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-1.217928507314312</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>6643</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>326.7879391794831</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>494</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>40.73448371625519</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>26.40102873469428</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.598897058187882</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>-6.037609793522932</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>6582</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>申豐</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>322.428039266248</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>51.70125704408211</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>24.05578276321781</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.8574275770932969</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>0.0357247385683947</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>6806</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>森崴能源</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>321.1806280133556</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>30.30810162010731</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>32.28363367198867</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>1.437623507568395</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>0.3767060656906009</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>6706</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>惠特</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>319.8451855910437</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>48.69595574494014</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>18.33759879254464</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.4565582620914242</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-3.936865684636677</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>6546</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>正基</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>312.9547032703164</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>50.17604797029433</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>18.79833936336457</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.305171469891753</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-0.7872609560339345</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>6641</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>基士德-KY</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>307.3953855107001</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>48.33883550074246</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>18.47475541857973</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>1.295478810426599</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0.010076981174512</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>6561</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>是方</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>301.597941943676</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>39.95310179169165</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>15.92831024669716</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.7831290660455803</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-2.415889121095163</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>6591</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>動力-KY</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>297.5295297100117</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>47.89571698016637</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>21.27229468791863</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0.3419286435501053</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>-0.1213228753602536</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>6794</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>向榮生技-創</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>292.1953224228291</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>43.80472455370605</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>12.3421806971738</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.9018978853386032</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>-0.2441823158338045</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>6655</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>科定</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>286.3466308157642</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>41.56732406472484</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>11.3868092559331</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0.4530174904144125</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-0.1615298829078009</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>6803</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>崑鼎</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>280.7227010509254</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>286.5</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>46.15617831811868</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>24.93383604328993</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>0.3365510385601423</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>0.0200492284719173</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>6568</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>宏觀</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>280.2611788583437</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>36.49207691973459</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>26.79358854175573</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.3773273955494983</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>-2.716731307425485</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>6739</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>279.4957356391664</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>40.01878436192246</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>13.15636385910696</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.4617560143540447</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-7.96328009818636</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>6741</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>91APP*-KY</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>274.5386283811026</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>47.23210500951463</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>11.56697746259884</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>0.3088788572932415</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-0.2008244012456962</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>6530</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>創威</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>273.3349459004269</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>43.42085234701366</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>15.37030248505064</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.5481834479056017</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>-1.258141815888457</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>6829</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>千附精密</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>272.7777222211289</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>48.70296765300441</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>15.22480620504827</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.8228802885376895</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>-1.221840131600894</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>6624</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>萬年清</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>264.4797919522783</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>50.84351011611045</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>12.87641141601794</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.1660141506019486</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>-0.8466583947305986</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>6671</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>三能-KY</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>264.1282557155092</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>31.28109326990326</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>16.53314465524487</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>1.13869551264866</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>0.0615953555498577</v>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>6689</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>伊雲谷</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>263.0097790658329</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>43.94801996005704</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>13.15457280986532</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0.6604450680510734</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>-0.2673178463243377</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>6550</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>北極星藥業-KY</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>257.9491049682562</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>39.19949754468562</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>34.80211484547163</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>0.7151758191876006</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>0.1882558760555894</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>6533</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>237.9493716166865</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>41.54824106436801</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>17.38626703298286</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>0.3659666306626591</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-1.991817398688603</v>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>6768</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>志強-KY</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>236.0692268231926</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>42.65018467420555</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>19.68857508131785</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.439277772592053</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>-0.9863750511687024</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>6534</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>正瀚-創</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>231.5122781301536</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>51.45026572332196</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>15.52807096553202</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0.2043133024836616</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>0.2146645791908981</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>6486</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>互動</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>219.7196600537474</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>44.91010668425125</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>17.18046689721345</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>0.4919923609059986</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>0.1066056059074328</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>6796</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>晉弘</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>210.6015728729433</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>40.60646693343379</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>30.94907525177072</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0.5849974715911801</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>0.297146230995819</v>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>6552</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>易華電</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>193.1053949052276</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>50.2543622094521</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>16.06653903305078</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.5920959602831702</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>-0.3735132207745319</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>6504</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>南六</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>189.5613741545583</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>38.29897723461637</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>19.12552846874458</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0.6915485751808468</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>0.0817778241864994</v>
-      </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>6577</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>勁豐</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>184.5927133941264</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>32.22666725827857</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>14.44189594914305</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>1.359271339412637</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-0.5273502491747291</v>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>6807</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>峰源-KY</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>176.0560341964963</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>33.65</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>44.56133179512</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>25.25671015176294</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0.5815075318441455</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>0.1995401502679753</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>6722</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>輝創</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>175.2247126256183</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>40.84784003316734</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>15.11452675435338</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>0.3261680613668061</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>-0.1130206901409136</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>6835</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>圓裕</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>160.2019229840527</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>42.5552187182104</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>13.96652691060163</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.1401610274202643</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>-0.1441846346349169</v>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>6674</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>鋐寶科技</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>155.3178938175574</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>45.9465259515588</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>17.1776694624163</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>0.6990016188308878</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>-0.0056636724478135</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>6838</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>台新藥</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>146.9956837223489</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>36.34457229431654</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>9.987312224858233</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.8223454801759448</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>0.0562771371694759</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>6541</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>泰福-KY</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>145.3276399708073</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>52.23109404744078</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>15.05479498000048</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.7868236035429527</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>0.0409418610394836</v>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
